--- a/resources/vega_models_withclasses.xlsx
+++ b/resources/vega_models_withclasses.xlsx
@@ -3100,9 +3100,6 @@
     <t>EC_FISHTOX</t>
   </si>
   <si>
-    <t>ED_(human)</t>
-  </si>
-  <si>
     <t>Reproductive_toxicity</t>
   </si>
   <si>
@@ -3122,6 +3119,9 @@
   </si>
   <si>
     <t>Skin_corrosion_irritation</t>
+  </si>
+  <si>
+    <t>Endocrine_disruption</t>
   </si>
 </sst>
 </file>
@@ -3705,7 +3705,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:N114" totalsRowShown="0">
-  <autoFilter ref="A1:N114"/>
+  <autoFilter ref="A1:N114">
+    <filterColumn colId="11">
+      <filters>
+        <filter val="ED_(human)"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState ref="A2:N114">
     <sortCondition ref="L1:L114"/>
   </sortState>
@@ -4053,7 +4059,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -4088,13 +4094,13 @@
         <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M2" t="s">
         <v>873</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -4126,13 +4132,13 @@
         <v>30</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M3" t="s">
         <v>873</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -4167,13 +4173,13 @@
         <v>38</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M4" t="s">
         <v>873</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -4208,13 +4214,13 @@
         <v>45</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M5" t="s">
         <v>873</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>197</v>
       </c>
@@ -4249,13 +4255,13 @@
         <v>204</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M6" t="s">
         <v>871</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>205</v>
       </c>
@@ -4291,13 +4297,13 @@
         <v>212</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M7" t="s">
         <v>871</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>213</v>
       </c>
@@ -4332,13 +4338,13 @@
         <v>204</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M8" t="s">
         <v>871</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>219</v>
       </c>
@@ -4374,13 +4380,13 @@
         <v>212</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M9" t="s">
         <v>871</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>226</v>
       </c>
@@ -4415,13 +4421,13 @@
         <v>232</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M10" t="s">
         <v>872</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>289</v>
       </c>
@@ -4457,13 +4463,13 @@
         <v>212</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M11" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>296</v>
       </c>
@@ -4498,13 +4504,13 @@
         <v>303</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M12" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>304</v>
       </c>
@@ -4540,13 +4546,13 @@
         <v>310</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M13" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>311</v>
       </c>
@@ -4578,13 +4584,13 @@
         <v>318</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M14" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>319</v>
       </c>
@@ -4620,13 +4626,13 @@
         <v>325</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M15" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>326</v>
       </c>
@@ -4661,13 +4667,13 @@
         <v>332</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M16" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>333</v>
       </c>
@@ -4702,13 +4708,13 @@
         <v>340</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M17" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>341</v>
       </c>
@@ -4743,13 +4749,13 @@
         <v>45</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M18" t="s">
         <v>874</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>355</v>
       </c>
@@ -4784,13 +4790,13 @@
         <v>303</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M19" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>499</v>
       </c>
@@ -4822,13 +4828,13 @@
         <v>506</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M20" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>507</v>
       </c>
@@ -4857,13 +4863,13 @@
         <v>513</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M21" t="s">
         <v>874</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>844</v>
       </c>
@@ -4892,13 +4898,13 @@
         <v>850</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M22" t="s">
         <v>1025</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>858</v>
       </c>
@@ -4933,13 +4939,13 @@
         <v>865</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M23" t="s">
         <v>1003</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>106</v>
       </c>
@@ -4977,7 +4983,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>124</v>
       </c>
@@ -5015,7 +5021,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>115</v>
       </c>
@@ -5053,7 +5059,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>133</v>
       </c>
@@ -5091,7 +5097,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>152</v>
       </c>
@@ -5129,7 +5135,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>160</v>
       </c>
@@ -5170,7 +5176,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>168</v>
       </c>
@@ -5208,7 +5214,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>175</v>
       </c>
@@ -5249,7 +5255,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>139</v>
       </c>
@@ -5287,7 +5293,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>146</v>
       </c>
@@ -5354,7 +5360,7 @@
         <v>54</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="M34" t="s">
         <v>1014</v>
@@ -5392,7 +5398,7 @@
         <v>62</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="M35" t="s">
         <v>1014</v>
@@ -5430,7 +5436,7 @@
         <v>354</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
@@ -5462,7 +5468,7 @@
         <v>581</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="M37" t="s">
         <v>1014</v>
@@ -5497,7 +5503,7 @@
         <v>581</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="M38" t="s">
         <v>1014</v>
@@ -5532,7 +5538,7 @@
         <v>581</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="M39" t="s">
         <v>1014</v>
@@ -5567,7 +5573,7 @@
         <v>581</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="M40" t="s">
         <v>1014</v>
@@ -5605,7 +5611,7 @@
         <v>639</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="M41" t="s">
         <v>1014</v>
@@ -5646,7 +5652,7 @@
         <v>658</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="M42" t="s">
         <v>1014</v>
@@ -5687,7 +5693,7 @@
         <v>447</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="M43" t="s">
         <v>1014</v>
@@ -5725,7 +5731,7 @@
         <v>672</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
@@ -5760,7 +5766,7 @@
         <v>680</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
@@ -5795,7 +5801,7 @@
         <v>687</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
@@ -5830,7 +5836,7 @@
         <v>797</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
@@ -5865,7 +5871,7 @@
         <v>804</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
@@ -5900,7 +5906,7 @@
         <v>811</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
@@ -5932,13 +5938,13 @@
         <v>835</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="M50" t="s">
         <v>1014</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>266</v>
       </c>
@@ -5967,13 +5973,13 @@
         <v>273</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M51" t="s">
         <v>1009</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>274</v>
       </c>
@@ -6005,13 +6011,13 @@
         <v>281</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M52" t="s">
         <v>1009</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>282</v>
       </c>
@@ -6043,13 +6049,13 @@
         <v>288</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M53" t="s">
         <v>1009</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>182</v>
       </c>
@@ -6087,7 +6093,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>483</v>
       </c>
@@ -6125,7 +6131,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>491</v>
       </c>
@@ -6163,7 +6169,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>514</v>
       </c>
@@ -6201,7 +6207,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>529</v>
       </c>
@@ -6239,7 +6245,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>522</v>
       </c>
@@ -6277,7 +6283,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>537</v>
       </c>
@@ -6315,7 +6321,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>545</v>
       </c>
@@ -6353,7 +6359,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>63</v>
       </c>
@@ -6388,13 +6394,13 @@
         <v>71</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M62" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>72</v>
       </c>
@@ -6429,13 +6435,13 @@
         <v>79</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M63" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>80</v>
       </c>
@@ -6470,13 +6476,13 @@
         <v>88</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M64" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>89</v>
       </c>
@@ -6511,13 +6517,13 @@
         <v>97</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M65" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>361</v>
       </c>
@@ -6552,13 +6558,13 @@
         <v>368</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M66" t="s">
         <v>877</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>377</v>
       </c>
@@ -6593,13 +6599,13 @@
         <v>384</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M67" t="s">
         <v>878</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>385</v>
       </c>
@@ -6634,13 +6640,13 @@
         <v>393</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M68" t="s">
         <v>879</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>394</v>
       </c>
@@ -6675,13 +6681,13 @@
         <v>401</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M69" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>448</v>
       </c>
@@ -6713,13 +6719,13 @@
         <v>454</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M70" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>455</v>
       </c>
@@ -6751,13 +6757,13 @@
         <v>454</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M71" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>476</v>
       </c>
@@ -6789,13 +6795,13 @@
         <v>454</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M72" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>688</v>
       </c>
@@ -6827,13 +6833,13 @@
         <v>695</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M73" t="s">
         <v>875</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>779</v>
       </c>
@@ -6868,13 +6874,13 @@
         <v>21</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M74" t="s">
         <v>998</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>785</v>
       </c>
@@ -6906,13 +6912,13 @@
         <v>30</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M75" t="s">
         <v>998</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>812</v>
       </c>
@@ -6951,7 +6957,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>820</v>
       </c>
@@ -6990,7 +6996,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>461</v>
       </c>
@@ -7028,7 +7034,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>469</v>
       </c>
@@ -7069,7 +7075,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>836</v>
       </c>
@@ -7107,7 +7113,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>851</v>
       </c>
@@ -7149,7 +7155,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>402</v>
       </c>
@@ -7190,7 +7196,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>582</v>
       </c>
@@ -7231,7 +7237,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>590</v>
       </c>
@@ -7272,7 +7278,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>597</v>
       </c>
@@ -7310,7 +7316,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>606</v>
       </c>
@@ -7351,7 +7357,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>612</v>
       </c>
@@ -7389,7 +7395,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>619</v>
       </c>
@@ -7430,7 +7436,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>625</v>
       </c>
@@ -7468,7 +7474,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>233</v>
       </c>
@@ -7500,13 +7506,13 @@
         <v>241</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M90" t="s">
         <v>1001</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>242</v>
       </c>
@@ -7538,13 +7544,13 @@
         <v>250</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M91" t="s">
         <v>1001</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>258</v>
       </c>
@@ -7573,13 +7579,13 @@
         <v>265</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M92" t="s">
         <v>1002</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>719</v>
       </c>
@@ -7608,13 +7614,13 @@
         <v>725</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="M93" t="s">
         <v>1006</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>726</v>
       </c>
@@ -7646,13 +7652,13 @@
         <v>733</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="M94" t="s">
         <v>1006</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>734</v>
       </c>
@@ -7684,13 +7690,13 @@
         <v>740</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="M95" t="s">
         <v>1006</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>696</v>
       </c>
@@ -7722,13 +7728,13 @@
         <v>704</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M96" t="s">
         <v>1007</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>712</v>
       </c>
@@ -7760,13 +7766,13 @@
         <v>718</v>
       </c>
       <c r="L97" s="4" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M97" t="s">
         <v>1007</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>705</v>
       </c>
@@ -7798,13 +7804,13 @@
         <v>711</v>
       </c>
       <c r="L98" s="4" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M98" t="s">
         <v>1007</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>755</v>
       </c>
@@ -7833,13 +7839,13 @@
         <v>762</v>
       </c>
       <c r="L99" s="4" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M99" t="s">
         <v>1007</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>763</v>
       </c>
@@ -7871,13 +7877,13 @@
         <v>770</v>
       </c>
       <c r="L100" s="4" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M100" t="s">
         <v>1007</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>771</v>
       </c>
@@ -7906,13 +7912,13 @@
         <v>778</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M101" t="s">
         <v>1007</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>426</v>
       </c>
@@ -7953,7 +7959,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>433</v>
       </c>
@@ -7994,7 +8000,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>418</v>
       </c>
@@ -8035,7 +8041,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>561</v>
       </c>
@@ -8076,7 +8082,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>568</v>
       </c>
@@ -8118,7 +8124,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>554</v>
       </c>
@@ -8159,7 +8165,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>190</v>
       </c>
@@ -8194,7 +8200,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>369</v>
       </c>
@@ -8232,7 +8238,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>410</v>
       </c>
@@ -8273,7 +8279,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>741</v>
       </c>
@@ -8317,7 +8323,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>749</v>
       </c>
@@ -8361,7 +8367,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>98</v>
       </c>
@@ -8402,7 +8408,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>251</v>
       </c>

--- a/resources/vega_models_withclasses.xlsx
+++ b/resources/vega_models_withclasses.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="1034">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="1034">
   <si>
     <t>Key</t>
   </si>
@@ -2626,9 +2626,6 @@
     <t>PMT</t>
   </si>
   <si>
-    <t>ENDPOINT_CATEORIES</t>
-  </si>
-  <si>
     <t>EC_FISHTOX_SECTION</t>
   </si>
   <si>
@@ -3122,6 +3119,9 @@
   </si>
   <si>
     <t>Endocrine_disruption</t>
+  </si>
+  <si>
+    <t>ENDPOINT_CATEGORY</t>
   </si>
 </sst>
 </file>
@@ -3705,15 +3705,9 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:N114" totalsRowShown="0">
-  <autoFilter ref="A1:N114">
-    <filterColumn colId="11">
-      <filters>
-        <filter val="ED_(human)"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <sortState ref="A2:N114">
-    <sortCondition ref="L1:L114"/>
+  <autoFilter ref="A1:N114"/>
+  <sortState ref="A34:N50">
+    <sortCondition ref="M1:M114"/>
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" name="Key"/>
@@ -3728,7 +3722,7 @@
     <tableColumn id="10" name="ADItemsName"/>
     <tableColumn id="11" name="ResultsName"/>
     <tableColumn id="12" name="SSbD" dataDxfId="0"/>
-    <tableColumn id="13" name="ENDPOINT_CATEORIES"/>
+    <tableColumn id="13" name="ENDPOINT_CATEGORY"/>
     <tableColumn id="14" name="Column1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4011,7 +4005,7 @@
     <col min="10" max="10" width="14.6640625" customWidth="1"/>
     <col min="11" max="11" width="66.77734375" customWidth="1"/>
     <col min="12" max="12" width="25.77734375" customWidth="1"/>
-    <col min="13" max="13" width="15.21875" customWidth="1"/>
+    <col min="13" max="13" width="35.33203125" customWidth="1"/>
     <col min="14" max="14" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4053,13 +4047,13 @@
         <v>866</v>
       </c>
       <c r="M1" t="s">
-        <v>868</v>
+        <v>1033</v>
       </c>
       <c r="N1" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -4094,13 +4088,13 @@
         <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M2" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -4132,13 +4126,13 @@
         <v>30</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M3" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -4173,13 +4167,13 @@
         <v>38</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M4" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -4214,13 +4208,13 @@
         <v>45</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M5" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>197</v>
       </c>
@@ -4255,13 +4249,13 @@
         <v>204</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M6" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>205</v>
       </c>
@@ -4297,13 +4291,13 @@
         <v>212</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M7" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>213</v>
       </c>
@@ -4338,13 +4332,13 @@
         <v>204</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M8" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>219</v>
       </c>
@@ -4380,13 +4374,13 @@
         <v>212</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M9" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>226</v>
       </c>
@@ -4421,13 +4415,13 @@
         <v>232</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M10" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>289</v>
       </c>
@@ -4463,13 +4457,13 @@
         <v>212</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M11" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>296</v>
       </c>
@@ -4504,13 +4498,13 @@
         <v>303</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M12" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>304</v>
       </c>
@@ -4546,13 +4540,13 @@
         <v>310</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M13" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>311</v>
       </c>
@@ -4584,13 +4578,13 @@
         <v>318</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M14" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>319</v>
       </c>
@@ -4626,13 +4620,13 @@
         <v>325</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M15" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>326</v>
       </c>
@@ -4667,13 +4661,13 @@
         <v>332</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M16" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>333</v>
       </c>
@@ -4708,13 +4702,13 @@
         <v>340</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M17" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>341</v>
       </c>
@@ -4749,13 +4743,13 @@
         <v>45</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M18" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>355</v>
       </c>
@@ -4790,13 +4784,13 @@
         <v>303</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M19" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>499</v>
       </c>
@@ -4828,13 +4822,13 @@
         <v>506</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M20" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>507</v>
       </c>
@@ -4863,13 +4857,13 @@
         <v>513</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M21" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>844</v>
       </c>
@@ -4898,13 +4892,13 @@
         <v>850</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M22" t="s">
-        <v>1025</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>858</v>
       </c>
@@ -4939,13 +4933,13 @@
         <v>865</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="M23" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>106</v>
       </c>
@@ -4977,13 +4971,13 @@
         <v>114</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="M24" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>124</v>
       </c>
@@ -5015,13 +5009,13 @@
         <v>132</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="M25" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>115</v>
       </c>
@@ -5053,13 +5047,13 @@
         <v>123</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="M26" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>133</v>
       </c>
@@ -5091,13 +5085,13 @@
         <v>114</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="M27" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>152</v>
       </c>
@@ -5129,13 +5123,13 @@
         <v>159</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="M28" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>160</v>
       </c>
@@ -5170,13 +5164,13 @@
         <v>167</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="M29" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>168</v>
       </c>
@@ -5208,13 +5202,13 @@
         <v>174</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="M30" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>175</v>
       </c>
@@ -5249,13 +5243,13 @@
         <v>181</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="M31" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>139</v>
       </c>
@@ -5287,13 +5281,13 @@
         <v>145</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="M32" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>146</v>
       </c>
@@ -5325,10 +5319,10 @@
         <v>145</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="M33" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
@@ -5360,10 +5354,10 @@
         <v>54</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="M34" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
@@ -5398,68 +5392,68 @@
         <v>62</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="M35" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>347</v>
+        <v>575</v>
       </c>
       <c r="B36" t="s">
-        <v>348</v>
+        <v>576</v>
       </c>
       <c r="C36" t="s">
-        <v>349</v>
+        <v>577</v>
       </c>
       <c r="D36" t="s">
-        <v>350</v>
-      </c>
-      <c r="E36" t="s">
-        <v>35</v>
+        <v>578</v>
       </c>
       <c r="F36" t="s">
-        <v>351</v>
+        <v>579</v>
       </c>
       <c r="G36" t="s">
-        <v>352</v>
+        <v>263</v>
       </c>
       <c r="H36" t="s">
-        <v>353</v>
+        <v>580</v>
       </c>
       <c r="I36" t="s">
         <v>53</v>
       </c>
       <c r="K36" t="s">
-        <v>354</v>
+        <v>581</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
+      </c>
+      <c r="M36" t="s">
+        <v>1013</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>575</v>
+        <v>640</v>
       </c>
       <c r="B37" t="s">
-        <v>576</v>
+        <v>641</v>
       </c>
       <c r="C37" t="s">
-        <v>577</v>
+        <v>642</v>
       </c>
       <c r="D37" t="s">
-        <v>578</v>
+        <v>643</v>
       </c>
       <c r="F37" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="G37" t="s">
         <v>263</v>
       </c>
       <c r="H37" t="s">
-        <v>580</v>
+        <v>645</v>
       </c>
       <c r="I37" t="s">
         <v>53</v>
@@ -5468,33 +5462,33 @@
         <v>581</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="M37" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="B38" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="C38" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="D38" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="F38" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="G38" t="s">
         <v>263</v>
       </c>
       <c r="H38" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="I38" t="s">
         <v>53</v>
@@ -5503,33 +5497,33 @@
         <v>581</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="M38" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>646</v>
+        <v>659</v>
       </c>
       <c r="B39" t="s">
-        <v>647</v>
+        <v>660</v>
       </c>
       <c r="C39" t="s">
-        <v>648</v>
+        <v>661</v>
       </c>
       <c r="D39" t="s">
-        <v>649</v>
+        <v>662</v>
       </c>
       <c r="F39" t="s">
-        <v>650</v>
+        <v>663</v>
       </c>
       <c r="G39" t="s">
         <v>263</v>
       </c>
       <c r="H39" t="s">
-        <v>651</v>
+        <v>664</v>
       </c>
       <c r="I39" t="s">
         <v>53</v>
@@ -5538,109 +5532,115 @@
         <v>581</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="M39" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>659</v>
+        <v>632</v>
       </c>
       <c r="B40" t="s">
-        <v>660</v>
+        <v>633</v>
       </c>
       <c r="C40" t="s">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="D40" t="s">
-        <v>662</v>
+        <v>635</v>
       </c>
       <c r="F40" t="s">
-        <v>663</v>
+        <v>636</v>
       </c>
       <c r="G40" t="s">
-        <v>263</v>
+        <v>637</v>
       </c>
       <c r="H40" t="s">
-        <v>664</v>
+        <v>638</v>
       </c>
       <c r="I40" t="s">
-        <v>53</v>
+        <v>19</v>
+      </c>
+      <c r="J40" t="s">
+        <v>29</v>
       </c>
       <c r="K40" t="s">
-        <v>581</v>
+        <v>639</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="M40" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
       <c r="B41" t="s">
-        <v>633</v>
+        <v>653</v>
       </c>
       <c r="C41" t="s">
-        <v>634</v>
+        <v>654</v>
       </c>
       <c r="D41" t="s">
-        <v>635</v>
+        <v>655</v>
+      </c>
+      <c r="E41" t="s">
+        <v>35</v>
       </c>
       <c r="F41" t="s">
-        <v>636</v>
+        <v>656</v>
       </c>
       <c r="G41" t="s">
-        <v>637</v>
+        <v>17</v>
       </c>
       <c r="H41" t="s">
-        <v>638</v>
+        <v>657</v>
       </c>
       <c r="I41" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="J41" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="K41" t="s">
-        <v>639</v>
+        <v>658</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="M41" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>652</v>
+        <v>441</v>
       </c>
       <c r="B42" t="s">
-        <v>653</v>
+        <v>442</v>
       </c>
       <c r="C42" t="s">
-        <v>654</v>
+        <v>443</v>
       </c>
       <c r="D42" t="s">
-        <v>655</v>
+        <v>444</v>
       </c>
       <c r="E42" t="s">
         <v>35</v>
       </c>
       <c r="F42" t="s">
-        <v>656</v>
+        <v>445</v>
       </c>
       <c r="G42" t="s">
         <v>17</v>
       </c>
       <c r="H42" t="s">
-        <v>657</v>
+        <v>446</v>
       </c>
       <c r="I42" t="s">
         <v>53</v>
@@ -5649,112 +5649,109 @@
         <v>20</v>
       </c>
       <c r="K42" t="s">
-        <v>658</v>
+        <v>447</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="M42" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>441</v>
+        <v>828</v>
       </c>
       <c r="B43" t="s">
-        <v>442</v>
+        <v>829</v>
       </c>
       <c r="C43" t="s">
-        <v>443</v>
+        <v>830</v>
       </c>
       <c r="D43" t="s">
-        <v>444</v>
-      </c>
-      <c r="E43" t="s">
-        <v>35</v>
+        <v>831</v>
       </c>
       <c r="F43" t="s">
-        <v>445</v>
+        <v>832</v>
       </c>
       <c r="G43" t="s">
-        <v>17</v>
+        <v>833</v>
       </c>
       <c r="H43" t="s">
-        <v>446</v>
+        <v>834</v>
       </c>
       <c r="I43" t="s">
-        <v>53</v>
-      </c>
-      <c r="J43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K43" t="s">
-        <v>447</v>
+        <v>835</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="M43" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>665</v>
+        <v>347</v>
       </c>
       <c r="B44" t="s">
-        <v>666</v>
+        <v>348</v>
       </c>
       <c r="C44" t="s">
-        <v>667</v>
+        <v>349</v>
       </c>
       <c r="D44" t="s">
-        <v>668</v>
+        <v>350</v>
+      </c>
+      <c r="E44" t="s">
+        <v>35</v>
       </c>
       <c r="F44" t="s">
-        <v>669</v>
+        <v>351</v>
       </c>
       <c r="G44" t="s">
-        <v>670</v>
+        <v>352</v>
       </c>
       <c r="H44" t="s">
-        <v>671</v>
+        <v>353</v>
       </c>
       <c r="I44" t="s">
-        <v>19</v>
-      </c>
-      <c r="J44" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="K44" t="s">
-        <v>672</v>
+        <v>354</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
+      </c>
+      <c r="M44" t="s">
+        <v>1013</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="B45" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="C45" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="D45" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="F45" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="G45" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="H45" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="I45" t="s">
         <v>19</v>
@@ -5763,138 +5760,150 @@
         <v>61</v>
       </c>
       <c r="K45" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
+      </c>
+      <c r="M45" t="s">
+        <v>1013</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="B46" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="C46" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D46" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="F46" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="G46" t="s">
-        <v>263</v>
+        <v>678</v>
       </c>
       <c r="H46" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="I46" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="J46" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="K46" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
+      </c>
+      <c r="M46" t="s">
+        <v>1013</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>791</v>
+        <v>681</v>
       </c>
       <c r="B47" t="s">
-        <v>792</v>
+        <v>682</v>
       </c>
       <c r="C47" t="s">
-        <v>793</v>
+        <v>683</v>
       </c>
       <c r="D47" t="s">
-        <v>794</v>
+        <v>684</v>
       </c>
       <c r="F47" t="s">
-        <v>795</v>
+        <v>685</v>
       </c>
       <c r="G47" t="s">
-        <v>768</v>
+        <v>263</v>
       </c>
       <c r="H47" t="s">
-        <v>796</v>
+        <v>686</v>
       </c>
       <c r="I47" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="J47" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="K47" t="s">
-        <v>797</v>
+        <v>687</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
+      </c>
+      <c r="M47" t="s">
+        <v>1013</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="B48" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="C48" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="D48" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="F48" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="G48" t="s">
-        <v>352</v>
+        <v>768</v>
       </c>
       <c r="H48" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="I48" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="J48" t="s">
         <v>61</v>
       </c>
       <c r="K48" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
+      </c>
+      <c r="M48" t="s">
+        <v>1013</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="B49" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="C49" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="D49" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="F49" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="G49" t="s">
         <v>352</v>
       </c>
       <c r="H49" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="I49" t="s">
         <v>19</v>
@@ -5903,48 +5912,54 @@
         <v>61</v>
       </c>
       <c r="K49" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
+      </c>
+      <c r="M49" t="s">
+        <v>1013</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>828</v>
+        <v>805</v>
       </c>
       <c r="B50" t="s">
-        <v>829</v>
+        <v>806</v>
       </c>
       <c r="C50" t="s">
-        <v>830</v>
+        <v>807</v>
       </c>
       <c r="D50" t="s">
-        <v>831</v>
+        <v>808</v>
       </c>
       <c r="F50" t="s">
-        <v>832</v>
+        <v>809</v>
       </c>
       <c r="G50" t="s">
-        <v>833</v>
+        <v>352</v>
       </c>
       <c r="H50" t="s">
-        <v>834</v>
+        <v>810</v>
       </c>
       <c r="I50" t="s">
         <v>19</v>
       </c>
+      <c r="J50" t="s">
+        <v>61</v>
+      </c>
       <c r="K50" t="s">
-        <v>835</v>
+        <v>811</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="M50" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>266</v>
       </c>
@@ -5973,13 +5988,13 @@
         <v>273</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M51" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>274</v>
       </c>
@@ -6011,13 +6026,13 @@
         <v>281</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M52" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>282</v>
       </c>
@@ -6049,13 +6064,13 @@
         <v>288</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M53" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>182</v>
       </c>
@@ -6087,13 +6102,13 @@
         <v>189</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="M54" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>483</v>
       </c>
@@ -6125,13 +6140,13 @@
         <v>490</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="M55" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>491</v>
       </c>
@@ -6163,13 +6178,13 @@
         <v>498</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="M56" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>514</v>
       </c>
@@ -6201,13 +6216,13 @@
         <v>521</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="M57" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>529</v>
       </c>
@@ -6239,13 +6254,13 @@
         <v>521</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="M58" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>522</v>
       </c>
@@ -6277,13 +6292,13 @@
         <v>521</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="M59" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>537</v>
       </c>
@@ -6315,13 +6330,13 @@
         <v>544</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="M60" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>545</v>
       </c>
@@ -6353,13 +6368,13 @@
         <v>553</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="M61" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>63</v>
       </c>
@@ -6394,13 +6409,13 @@
         <v>71</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M62" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>72</v>
       </c>
@@ -6435,13 +6450,13 @@
         <v>79</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M63" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>80</v>
       </c>
@@ -6476,13 +6491,13 @@
         <v>88</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M64" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>89</v>
       </c>
@@ -6517,13 +6532,13 @@
         <v>97</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M65" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>361</v>
       </c>
@@ -6558,13 +6573,13 @@
         <v>368</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M66" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>377</v>
       </c>
@@ -6599,13 +6614,13 @@
         <v>384</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M67" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>385</v>
       </c>
@@ -6640,13 +6655,13 @@
         <v>393</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M68" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>394</v>
       </c>
@@ -6681,13 +6696,13 @@
         <v>401</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M69" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>448</v>
       </c>
@@ -6719,13 +6734,13 @@
         <v>454</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M70" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>455</v>
       </c>
@@ -6757,13 +6772,13 @@
         <v>454</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M71" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>476</v>
       </c>
@@ -6795,13 +6810,13 @@
         <v>454</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M72" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>688</v>
       </c>
@@ -6833,13 +6848,13 @@
         <v>695</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M73" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>779</v>
       </c>
@@ -6874,13 +6889,13 @@
         <v>21</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M74" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>785</v>
       </c>
@@ -6912,13 +6927,13 @@
         <v>30</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M75" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>812</v>
       </c>
@@ -6953,11 +6968,14 @@
         <v>819</v>
       </c>
       <c r="L76" s="1"/>
+      <c r="M76" t="s">
+        <v>881</v>
+      </c>
       <c r="N76" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>820</v>
       </c>
@@ -6992,11 +7010,14 @@
         <v>827</v>
       </c>
       <c r="L77" s="1"/>
+      <c r="M77" t="s">
+        <v>881</v>
+      </c>
       <c r="N77" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>461</v>
       </c>
@@ -7028,13 +7049,13 @@
         <v>468</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="M78" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>469</v>
       </c>
@@ -7069,13 +7090,13 @@
         <v>475</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="M79" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>836</v>
       </c>
@@ -7107,13 +7128,13 @@
         <v>843</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="M80" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>851</v>
       </c>
@@ -7149,13 +7170,13 @@
         <v>857</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="M81" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>402</v>
       </c>
@@ -7193,10 +7214,10 @@
         <v>867</v>
       </c>
       <c r="M82" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>582</v>
       </c>
@@ -7234,10 +7255,10 @@
         <v>867</v>
       </c>
       <c r="M83" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>590</v>
       </c>
@@ -7275,10 +7296,10 @@
         <v>867</v>
       </c>
       <c r="M84" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>597</v>
       </c>
@@ -7313,10 +7334,10 @@
         <v>867</v>
       </c>
       <c r="M85" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>606</v>
       </c>
@@ -7354,10 +7375,10 @@
         <v>867</v>
       </c>
       <c r="M86" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>612</v>
       </c>
@@ -7392,10 +7413,10 @@
         <v>867</v>
       </c>
       <c r="M87" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>619</v>
       </c>
@@ -7433,10 +7454,10 @@
         <v>867</v>
       </c>
       <c r="M88" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>625</v>
       </c>
@@ -7471,10 +7492,10 @@
         <v>867</v>
       </c>
       <c r="M89" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>233</v>
       </c>
@@ -7506,13 +7527,13 @@
         <v>241</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="M90" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>242</v>
       </c>
@@ -7544,13 +7565,13 @@
         <v>250</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="M91" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>258</v>
       </c>
@@ -7579,13 +7600,13 @@
         <v>265</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="M92" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>719</v>
       </c>
@@ -7614,13 +7635,13 @@
         <v>725</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M93" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>726</v>
       </c>
@@ -7652,13 +7673,13 @@
         <v>733</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M94" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>734</v>
       </c>
@@ -7690,13 +7711,13 @@
         <v>740</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M95" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>696</v>
       </c>
@@ -7728,13 +7749,13 @@
         <v>704</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M96" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>712</v>
       </c>
@@ -7766,13 +7787,13 @@
         <v>718</v>
       </c>
       <c r="L97" s="4" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M97" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>705</v>
       </c>
@@ -7804,13 +7825,13 @@
         <v>711</v>
       </c>
       <c r="L98" s="4" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M98" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>755</v>
       </c>
@@ -7839,13 +7860,13 @@
         <v>762</v>
       </c>
       <c r="L99" s="4" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M99" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>763</v>
       </c>
@@ -7877,13 +7898,13 @@
         <v>770</v>
       </c>
       <c r="L100" s="4" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M100" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>771</v>
       </c>
@@ -7912,13 +7933,13 @@
         <v>778</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M101" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>426</v>
       </c>
@@ -7953,13 +7974,13 @@
         <v>432</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="M102" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>433</v>
       </c>
@@ -7994,13 +8015,13 @@
         <v>440</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="M103" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>418</v>
       </c>
@@ -8035,13 +8056,13 @@
         <v>425</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="M104" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="105" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>561</v>
       </c>
@@ -8076,13 +8097,13 @@
         <v>567</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="M105" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="106" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>568</v>
       </c>
@@ -8118,13 +8139,13 @@
         <v>574</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="M106" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="107" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>554</v>
       </c>
@@ -8159,13 +8180,13 @@
         <v>560</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="M107" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="108" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>190</v>
       </c>
@@ -8194,13 +8215,13 @@
         <v>196</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="M108" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="109" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>369</v>
       </c>
@@ -8232,13 +8253,13 @@
         <v>376</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="M109" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="110" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>410</v>
       </c>
@@ -8273,13 +8294,13 @@
         <v>417</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="M110" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="111" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>741</v>
       </c>
@@ -8314,16 +8335,16 @@
         <v>748</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="M111" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="N111" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="112" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>749</v>
       </c>
@@ -8358,16 +8379,16 @@
         <v>748</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="M112" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="N112" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="113" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>98</v>
       </c>
@@ -8399,16 +8420,16 @@
         <v>105</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="M113" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="N113" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="114" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>251</v>
       </c>
@@ -8441,13 +8462,13 @@
         <v>257</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="M114" t="s">
+        <v>1003</v>
+      </c>
+      <c r="N114" t="s">
         <v>1004</v>
-      </c>
-      <c r="N114" t="s">
-        <v>1005</v>
       </c>
     </row>
   </sheetData>
@@ -8469,458 +8490,458 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>995</v>
+      </c>
+      <c r="B1" t="s">
         <v>996</v>
-      </c>
-      <c r="B1" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>884</v>
+      </c>
+      <c r="B2" t="s">
         <v>885</v>
-      </c>
-      <c r="B2" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>886</v>
+      </c>
+      <c r="B3" t="s">
         <v>887</v>
-      </c>
-      <c r="B3" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>888</v>
+      </c>
+      <c r="B4" t="s">
         <v>889</v>
-      </c>
-      <c r="B4" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>890</v>
+      </c>
+      <c r="B5" t="s">
         <v>891</v>
-      </c>
-      <c r="B5" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>892</v>
+      </c>
+      <c r="B6" t="s">
         <v>893</v>
-      </c>
-      <c r="B6" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>894</v>
+      </c>
+      <c r="B7" t="s">
         <v>895</v>
-      </c>
-      <c r="B7" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>896</v>
+      </c>
+      <c r="B8" t="s">
         <v>897</v>
-      </c>
-      <c r="B8" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>898</v>
+      </c>
+      <c r="B9" t="s">
         <v>899</v>
-      </c>
-      <c r="B9" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>900</v>
+      </c>
+      <c r="B10" t="s">
         <v>901</v>
-      </c>
-      <c r="B10" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>902</v>
+      </c>
+      <c r="B11" t="s">
         <v>903</v>
-      </c>
-      <c r="B11" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>904</v>
+      </c>
+      <c r="B12" t="s">
         <v>905</v>
-      </c>
-      <c r="B12" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>906</v>
+      </c>
+      <c r="B13" t="s">
         <v>907</v>
-      </c>
-      <c r="B13" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>908</v>
+      </c>
+      <c r="B14" t="s">
         <v>909</v>
-      </c>
-      <c r="B14" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>910</v>
+      </c>
+      <c r="B15" t="s">
         <v>911</v>
-      </c>
-      <c r="B15" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>912</v>
+      </c>
+      <c r="B16" t="s">
         <v>913</v>
-      </c>
-      <c r="B16" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>914</v>
+      </c>
+      <c r="B17" t="s">
         <v>915</v>
-      </c>
-      <c r="B17" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>916</v>
+      </c>
+      <c r="B18" t="s">
         <v>917</v>
-      </c>
-      <c r="B18" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>918</v>
+      </c>
+      <c r="B19" t="s">
         <v>919</v>
-      </c>
-      <c r="B19" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>920</v>
+      </c>
+      <c r="B20" t="s">
         <v>921</v>
-      </c>
-      <c r="B20" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>922</v>
+      </c>
+      <c r="B21" t="s">
         <v>923</v>
-      </c>
-      <c r="B21" t="s">
-        <v>924</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>924</v>
+      </c>
+      <c r="B22" t="s">
         <v>925</v>
-      </c>
-      <c r="B22" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>926</v>
+      </c>
+      <c r="B23" t="s">
         <v>927</v>
-      </c>
-      <c r="B23" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>928</v>
+      </c>
+      <c r="B24" t="s">
         <v>929</v>
-      </c>
-      <c r="B24" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>930</v>
+      </c>
+      <c r="B25" t="s">
         <v>931</v>
-      </c>
-      <c r="B25" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>932</v>
+      </c>
+      <c r="B26" t="s">
         <v>933</v>
-      </c>
-      <c r="B26" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>934</v>
+      </c>
+      <c r="B27" t="s">
         <v>935</v>
-      </c>
-      <c r="B27" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>936</v>
+      </c>
+      <c r="B28" t="s">
         <v>937</v>
-      </c>
-      <c r="B28" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>938</v>
+      </c>
+      <c r="B29" t="s">
         <v>939</v>
-      </c>
-      <c r="B29" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>940</v>
+      </c>
+      <c r="B30" t="s">
         <v>941</v>
-      </c>
-      <c r="B30" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>942</v>
+      </c>
+      <c r="B31" t="s">
         <v>943</v>
-      </c>
-      <c r="B31" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>944</v>
+      </c>
+      <c r="B32" t="s">
         <v>945</v>
-      </c>
-      <c r="B32" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>946</v>
+      </c>
+      <c r="B33" t="s">
         <v>947</v>
-      </c>
-      <c r="B33" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>948</v>
+      </c>
+      <c r="B34" t="s">
         <v>949</v>
-      </c>
-      <c r="B34" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>950</v>
+      </c>
+      <c r="B35" t="s">
         <v>951</v>
-      </c>
-      <c r="B35" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>952</v>
+      </c>
+      <c r="B36" t="s">
         <v>953</v>
-      </c>
-      <c r="B36" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>954</v>
+      </c>
+      <c r="B37" t="s">
         <v>955</v>
-      </c>
-      <c r="B37" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>956</v>
+      </c>
+      <c r="B38" t="s">
         <v>957</v>
-      </c>
-      <c r="B38" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>958</v>
+      </c>
+      <c r="B39" t="s">
         <v>959</v>
-      </c>
-      <c r="B39" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>960</v>
+      </c>
+      <c r="B40" t="s">
         <v>961</v>
-      </c>
-      <c r="B40" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>962</v>
+      </c>
+      <c r="B41" t="s">
         <v>963</v>
-      </c>
-      <c r="B41" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>964</v>
+      </c>
+      <c r="B42" t="s">
         <v>965</v>
-      </c>
-      <c r="B42" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>966</v>
+      </c>
+      <c r="B43" t="s">
         <v>967</v>
-      </c>
-      <c r="B43" t="s">
-        <v>968</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>968</v>
+      </c>
+      <c r="B44" t="s">
         <v>969</v>
-      </c>
-      <c r="B44" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>970</v>
+      </c>
+      <c r="B45" t="s">
         <v>971</v>
-      </c>
-      <c r="B45" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>972</v>
+      </c>
+      <c r="B46" t="s">
         <v>973</v>
-      </c>
-      <c r="B46" t="s">
-        <v>974</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>974</v>
+      </c>
+      <c r="B47" t="s">
         <v>975</v>
-      </c>
-      <c r="B47" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>976</v>
+      </c>
+      <c r="B48" t="s">
         <v>977</v>
-      </c>
-      <c r="B48" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>978</v>
+      </c>
+      <c r="B49" t="s">
         <v>979</v>
-      </c>
-      <c r="B49" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>980</v>
+      </c>
+      <c r="B50" t="s">
         <v>981</v>
-      </c>
-      <c r="B50" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>982</v>
+      </c>
+      <c r="B51" t="s">
         <v>983</v>
-      </c>
-      <c r="B51" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>984</v>
+      </c>
+      <c r="B52" t="s">
         <v>985</v>
-      </c>
-      <c r="B52" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>986</v>
+      </c>
+      <c r="B53" t="s">
         <v>987</v>
-      </c>
-      <c r="B53" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B54" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>989</v>
+      </c>
+      <c r="B55" t="s">
         <v>990</v>
-      </c>
-      <c r="B55" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>991</v>
+      </c>
+      <c r="B56" t="s">
         <v>992</v>
-      </c>
-      <c r="B56" t="s">
-        <v>993</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>993</v>
+      </c>
+      <c r="B57" t="s">
         <v>994</v>
-      </c>
-      <c r="B57" t="s">
-        <v>995</v>
       </c>
     </row>
   </sheetData>

--- a/resources/vega_models_withclasses.xlsx
+++ b/resources/vega_models_withclasses.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nina\src\git_idea\toxpredict-cp\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nina\src\git_idea\qubounds\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -331,9 +331,6 @@
     <t>KNN model for bee contact and oral acute toxicity</t>
   </si>
   <si>
-    <t>{0.0=Strong toxicity (lower than 1 Âµg/bee), 1.0=Moderate toxicity (between 1 and 100 Âµg/bee), 2.0=Low toxicity (over 100 Âµg/bee), -999.0=Non Predicted}</t>
-  </si>
-  <si>
     <t>{HasAlerts=False, TS=/data/ts_bee_knn.dat}</t>
   </si>
   <si>
@@ -3122,6 +3119,9 @@
   </si>
   <si>
     <t>ENDPOINT_CATEGORY</t>
+  </si>
+  <si>
+    <t>{0.0=Strong toxicity (lower than 1 µg/bee), 1.0=Moderate toxicity (between 1 and 100 µg/bee), 2.0=Low toxicity (over 100 µg/bee), -999.0=Non Predicted}</t>
   </si>
 </sst>
 </file>
@@ -4044,13 +4044,13 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="M1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="N1" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -4088,10 +4088,10 @@
         <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -4126,10 +4126,10 @@
         <v>30</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M3" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -4167,10 +4167,10 @@
         <v>38</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -4208,407 +4208,407 @@
         <v>45</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M5" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B6" t="s">
         <v>197</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>198</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>199</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>200</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>201</v>
-      </c>
-      <c r="F6" t="s">
-        <v>202</v>
       </c>
       <c r="G6" t="s">
         <v>17</v>
       </c>
       <c r="H6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J6" t="s">
         <v>20</v>
       </c>
       <c r="K6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M6" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7" t="s">
         <v>205</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>206</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>207</v>
-      </c>
-      <c r="D7" t="s">
-        <v>208</v>
       </c>
       <c r="E7" t="e">
         <f>-LOG(mol/l)</f>
         <v>#NAME?</v>
       </c>
       <c r="F7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G7" t="s">
         <v>17</v>
       </c>
       <c r="H7" t="s">
+        <v>209</v>
+      </c>
+      <c r="I7" t="s">
         <v>210</v>
-      </c>
-      <c r="I7" t="s">
-        <v>211</v>
       </c>
       <c r="J7" t="s">
         <v>20</v>
       </c>
       <c r="K7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M7" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>212</v>
+      </c>
+      <c r="B8" t="s">
         <v>213</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>214</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>215</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F8" t="s">
         <v>216</v>
-      </c>
-      <c r="E8" t="s">
-        <v>201</v>
-      </c>
-      <c r="F8" t="s">
-        <v>217</v>
       </c>
       <c r="G8" t="s">
         <v>17</v>
       </c>
       <c r="H8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J8" t="s">
         <v>20</v>
       </c>
       <c r="K8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M8" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B9" t="s">
         <v>219</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>220</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>221</v>
-      </c>
-      <c r="D9" t="s">
-        <v>222</v>
       </c>
       <c r="E9" t="e">
         <f>-LOG(mol/l)</f>
         <v>#NAME?</v>
       </c>
       <c r="F9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G9" t="s">
         <v>17</v>
       </c>
       <c r="H9" t="s">
+        <v>223</v>
+      </c>
+      <c r="I9" t="s">
         <v>224</v>
-      </c>
-      <c r="I9" t="s">
-        <v>225</v>
       </c>
       <c r="J9" t="s">
         <v>20</v>
       </c>
       <c r="K9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M9" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>225</v>
+      </c>
+      <c r="B10" t="s">
         <v>226</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>227</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>228</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
+        <v>200</v>
+      </c>
+      <c r="F10" t="s">
         <v>229</v>
-      </c>
-      <c r="E10" t="s">
-        <v>201</v>
-      </c>
-      <c r="F10" t="s">
-        <v>230</v>
       </c>
       <c r="G10" t="s">
         <v>17</v>
       </c>
       <c r="H10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J10" t="s">
         <v>20</v>
       </c>
       <c r="K10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M10" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>288</v>
+      </c>
+      <c r="B11" t="s">
         <v>289</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>290</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>291</v>
-      </c>
-      <c r="D11" t="s">
-        <v>292</v>
       </c>
       <c r="E11" t="e">
         <f>-LOG(mol/l)</f>
         <v>#NAME?</v>
       </c>
       <c r="F11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G11" t="s">
         <v>17</v>
       </c>
       <c r="H11" t="s">
+        <v>293</v>
+      </c>
+      <c r="I11" t="s">
         <v>294</v>
-      </c>
-      <c r="I11" t="s">
-        <v>295</v>
       </c>
       <c r="J11" t="s">
         <v>20</v>
       </c>
       <c r="K11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M11" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>295</v>
+      </c>
+      <c r="B12" t="s">
         <v>296</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>297</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>298</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>299</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>300</v>
-      </c>
-      <c r="F12" t="s">
-        <v>301</v>
       </c>
       <c r="G12" t="s">
         <v>17</v>
       </c>
       <c r="H12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J12" t="s">
         <v>87</v>
       </c>
       <c r="K12" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M12" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>303</v>
+      </c>
+      <c r="B13" t="s">
         <v>304</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>305</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>306</v>
-      </c>
-      <c r="D13" t="s">
-        <v>307</v>
       </c>
       <c r="E13" t="e">
         <f>-LOG(mmol/l)</f>
         <v>#NAME?</v>
       </c>
       <c r="F13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G13" t="s">
         <v>17</v>
       </c>
       <c r="H13" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J13" t="s">
         <v>20</v>
       </c>
       <c r="K13" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>310</v>
+      </c>
+      <c r="B14" t="s">
         <v>311</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>312</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>313</v>
       </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
         <v>314</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>315</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>316</v>
       </c>
-      <c r="H14" t="s">
-        <v>317</v>
-      </c>
       <c r="I14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J14" t="s">
         <v>61</v>
       </c>
       <c r="K14" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M14" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>318</v>
+      </c>
+      <c r="B15" t="s">
         <v>319</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>320</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>321</v>
-      </c>
-      <c r="D15" t="s">
-        <v>322</v>
       </c>
       <c r="E15" t="e">
         <f>-LOG(mg/l)</f>
         <v>#NAME?</v>
       </c>
       <c r="F15" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G15" t="s">
         <v>17</v>
       </c>
       <c r="H15" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I15" t="s">
         <v>19</v>
@@ -4617,124 +4617,124 @@
         <v>87</v>
       </c>
       <c r="K15" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M15" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>325</v>
+      </c>
+      <c r="B16" t="s">
         <v>326</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>327</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>328</v>
-      </c>
-      <c r="D16" t="s">
-        <v>329</v>
       </c>
       <c r="E16" t="s">
         <v>35</v>
       </c>
       <c r="F16" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G16" t="s">
         <v>17</v>
       </c>
       <c r="H16" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J16" t="s">
         <v>20</v>
       </c>
       <c r="K16" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M16" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>332</v>
+      </c>
+      <c r="B17" t="s">
         <v>333</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>334</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>335</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>336</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>337</v>
-      </c>
-      <c r="F17" t="s">
-        <v>338</v>
       </c>
       <c r="G17" t="s">
         <v>17</v>
       </c>
       <c r="H17" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J17" t="s">
         <v>20</v>
       </c>
       <c r="K17" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M17" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>340</v>
+      </c>
+      <c r="B18" t="s">
         <v>341</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>342</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>343</v>
-      </c>
-      <c r="D18" t="s">
-        <v>344</v>
       </c>
       <c r="E18" t="s">
         <v>35</v>
       </c>
       <c r="F18" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G18" t="s">
         <v>17</v>
       </c>
       <c r="H18" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="I18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J18" t="s">
         <v>20</v>
@@ -4743,185 +4743,185 @@
         <v>45</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M18" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>354</v>
+      </c>
+      <c r="B19" t="s">
         <v>355</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>356</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>357</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
+        <v>299</v>
+      </c>
+      <c r="F19" t="s">
         <v>358</v>
-      </c>
-      <c r="E19" t="s">
-        <v>300</v>
-      </c>
-      <c r="F19" t="s">
-        <v>359</v>
       </c>
       <c r="G19" t="s">
         <v>17</v>
       </c>
       <c r="H19" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="I19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J19" t="s">
         <v>87</v>
       </c>
       <c r="K19" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M19" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>498</v>
+      </c>
+      <c r="B20" t="s">
         <v>499</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>500</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>501</v>
       </c>
-      <c r="D20" t="s">
+      <c r="F20" t="s">
         <v>502</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>503</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>504</v>
       </c>
-      <c r="H20" t="s">
-        <v>505</v>
-      </c>
       <c r="I20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J20" t="s">
         <v>29</v>
       </c>
       <c r="K20" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M20" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>506</v>
+      </c>
+      <c r="B21" t="s">
         <v>507</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>508</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>509</v>
       </c>
-      <c r="D21" t="s">
+      <c r="F21" t="s">
+        <v>508</v>
+      </c>
+      <c r="G21" t="s">
         <v>510</v>
       </c>
-      <c r="F21" t="s">
-        <v>509</v>
-      </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>511</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
+        <v>112</v>
+      </c>
+      <c r="K21" t="s">
         <v>512</v>
       </c>
-      <c r="I21" t="s">
-        <v>113</v>
-      </c>
-      <c r="K21" t="s">
-        <v>513</v>
-      </c>
       <c r="L21" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M21" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>843</v>
+      </c>
+      <c r="B22" t="s">
         <v>844</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>845</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>846</v>
       </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
         <v>847</v>
-      </c>
-      <c r="F22" t="s">
-        <v>848</v>
       </c>
       <c r="G22" t="s">
         <v>17</v>
       </c>
       <c r="H22" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="I22" t="s">
         <v>19</v>
       </c>
       <c r="K22" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M22" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>857</v>
+      </c>
+      <c r="B23" t="s">
         <v>858</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>859</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>860</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>861</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>862</v>
-      </c>
-      <c r="F23" t="s">
-        <v>863</v>
       </c>
       <c r="G23" t="s">
         <v>17</v>
       </c>
       <c r="H23" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="I23" t="s">
         <v>19</v>
@@ -4930,188 +4930,188 @@
         <v>20</v>
       </c>
       <c r="K23" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="M23" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B24" t="s">
         <v>106</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>107</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>108</v>
       </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
         <v>109</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>110</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>111</v>
       </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>112</v>
-      </c>
-      <c r="I24" t="s">
-        <v>113</v>
       </c>
       <c r="J24" t="s">
         <v>61</v>
       </c>
       <c r="K24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="M24" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>123</v>
+      </c>
+      <c r="B25" t="s">
         <v>124</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>125</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>126</v>
       </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
         <v>127</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
+        <v>119</v>
+      </c>
+      <c r="H25" t="s">
         <v>128</v>
       </c>
-      <c r="G25" t="s">
-        <v>120</v>
-      </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>129</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>130</v>
       </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>131</v>
       </c>
-      <c r="K25" t="s">
-        <v>132</v>
-      </c>
       <c r="L25" s="3" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="M25" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>114</v>
+      </c>
+      <c r="B26" t="s">
         <v>115</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>116</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>117</v>
       </c>
-      <c r="D26" t="s">
+      <c r="F26" t="s">
         <v>118</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>119</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>120</v>
       </c>
-      <c r="H26" t="s">
+      <c r="I26" t="s">
         <v>121</v>
-      </c>
-      <c r="I26" t="s">
-        <v>122</v>
       </c>
       <c r="J26" t="s">
         <v>61</v>
       </c>
       <c r="K26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="M26" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>132</v>
+      </c>
+      <c r="B27" t="s">
         <v>133</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>134</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>135</v>
       </c>
-      <c r="D27" t="s">
+      <c r="F27" t="s">
         <v>136</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
+        <v>110</v>
+      </c>
+      <c r="H27" t="s">
         <v>137</v>
       </c>
-      <c r="G27" t="s">
-        <v>111</v>
-      </c>
-      <c r="H27" t="s">
-        <v>138</v>
-      </c>
       <c r="I27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J27" t="s">
         <v>61</v>
       </c>
       <c r="K27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="M27" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>151</v>
+      </c>
+      <c r="B28" t="s">
         <v>152</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>153</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>154</v>
       </c>
-      <c r="D28" t="s">
+      <c r="F28" t="s">
         <v>155</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>156</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>157</v>
-      </c>
-      <c r="H28" t="s">
-        <v>158</v>
       </c>
       <c r="I28" t="s">
         <v>19</v>
@@ -5120,39 +5120,39 @@
         <v>29</v>
       </c>
       <c r="K28" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="M28" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>159</v>
+      </c>
+      <c r="B29" t="s">
         <v>160</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>161</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>162</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>163</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>164</v>
-      </c>
-      <c r="F29" t="s">
-        <v>165</v>
       </c>
       <c r="G29" t="s">
         <v>17</v>
       </c>
       <c r="H29" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I29" t="s">
         <v>19</v>
@@ -5161,36 +5161,36 @@
         <v>20</v>
       </c>
       <c r="K29" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="M29" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>167</v>
+      </c>
+      <c r="B30" t="s">
         <v>168</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>169</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>170</v>
       </c>
-      <c r="D30" t="s">
+      <c r="F30" t="s">
         <v>171</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
+        <v>156</v>
+      </c>
+      <c r="H30" t="s">
         <v>172</v>
-      </c>
-      <c r="G30" t="s">
-        <v>157</v>
-      </c>
-      <c r="H30" t="s">
-        <v>173</v>
       </c>
       <c r="I30" t="s">
         <v>19</v>
@@ -5199,39 +5199,39 @@
         <v>29</v>
       </c>
       <c r="K30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="M30" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B31" t="s">
         <v>175</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>176</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>177</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
+        <v>163</v>
+      </c>
+      <c r="F31" t="s">
         <v>178</v>
-      </c>
-      <c r="E31" t="s">
-        <v>164</v>
-      </c>
-      <c r="F31" t="s">
-        <v>179</v>
       </c>
       <c r="G31" t="s">
         <v>17</v>
       </c>
       <c r="H31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I31" t="s">
         <v>19</v>
@@ -5240,36 +5240,36 @@
         <v>20</v>
       </c>
       <c r="K31" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="M31" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>138</v>
+      </c>
+      <c r="B32" t="s">
         <v>139</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>140</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>141</v>
       </c>
-      <c r="D32" t="s">
+      <c r="F32" t="s">
         <v>142</v>
-      </c>
-      <c r="F32" t="s">
-        <v>143</v>
       </c>
       <c r="G32" t="s">
         <v>17</v>
       </c>
       <c r="H32" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I32" t="s">
         <v>53</v>
@@ -5278,36 +5278,36 @@
         <v>61</v>
       </c>
       <c r="K32" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="M32" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>145</v>
+      </c>
+      <c r="B33" t="s">
         <v>146</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>147</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>148</v>
       </c>
-      <c r="D33" t="s">
+      <c r="F33" t="s">
         <v>149</v>
-      </c>
-      <c r="F33" t="s">
-        <v>150</v>
       </c>
       <c r="G33" t="s">
         <v>17</v>
       </c>
       <c r="H33" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I33" t="s">
         <v>53</v>
@@ -5316,13 +5316,13 @@
         <v>61</v>
       </c>
       <c r="K33" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="M33" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
@@ -5354,10 +5354,10 @@
         <v>54</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M34" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
@@ -5392,173 +5392,173 @@
         <v>62</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M35" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>574</v>
+      </c>
+      <c r="B36" t="s">
         <v>575</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>576</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>577</v>
       </c>
-      <c r="D36" t="s">
+      <c r="F36" t="s">
         <v>578</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
+        <v>262</v>
+      </c>
+      <c r="H36" t="s">
         <v>579</v>
-      </c>
-      <c r="G36" t="s">
-        <v>263</v>
-      </c>
-      <c r="H36" t="s">
-        <v>580</v>
       </c>
       <c r="I36" t="s">
         <v>53</v>
       </c>
       <c r="K36" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M36" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>639</v>
+      </c>
+      <c r="B37" t="s">
         <v>640</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>641</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>642</v>
       </c>
-      <c r="D37" t="s">
+      <c r="F37" t="s">
         <v>643</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
+        <v>262</v>
+      </c>
+      <c r="H37" t="s">
         <v>644</v>
-      </c>
-      <c r="G37" t="s">
-        <v>263</v>
-      </c>
-      <c r="H37" t="s">
-        <v>645</v>
       </c>
       <c r="I37" t="s">
         <v>53</v>
       </c>
       <c r="K37" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M37" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>645</v>
+      </c>
+      <c r="B38" t="s">
         <v>646</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>647</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>648</v>
       </c>
-      <c r="D38" t="s">
+      <c r="F38" t="s">
         <v>649</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
+        <v>262</v>
+      </c>
+      <c r="H38" t="s">
         <v>650</v>
-      </c>
-      <c r="G38" t="s">
-        <v>263</v>
-      </c>
-      <c r="H38" t="s">
-        <v>651</v>
       </c>
       <c r="I38" t="s">
         <v>53</v>
       </c>
       <c r="K38" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M38" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>658</v>
+      </c>
+      <c r="B39" t="s">
         <v>659</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>660</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>661</v>
       </c>
-      <c r="D39" t="s">
+      <c r="F39" t="s">
         <v>662</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
+        <v>262</v>
+      </c>
+      <c r="H39" t="s">
         <v>663</v>
-      </c>
-      <c r="G39" t="s">
-        <v>263</v>
-      </c>
-      <c r="H39" t="s">
-        <v>664</v>
       </c>
       <c r="I39" t="s">
         <v>53</v>
       </c>
       <c r="K39" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M39" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>631</v>
+      </c>
+      <c r="B40" t="s">
         <v>632</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>633</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>634</v>
       </c>
-      <c r="D40" t="s">
+      <c r="F40" t="s">
         <v>635</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>636</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>637</v>
-      </c>
-      <c r="H40" t="s">
-        <v>638</v>
       </c>
       <c r="I40" t="s">
         <v>19</v>
@@ -5567,39 +5567,39 @@
         <v>29</v>
       </c>
       <c r="K40" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M40" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>651</v>
+      </c>
+      <c r="B41" t="s">
         <v>652</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>653</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>654</v>
-      </c>
-      <c r="D41" t="s">
-        <v>655</v>
       </c>
       <c r="E41" t="s">
         <v>35</v>
       </c>
       <c r="F41" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G41" t="s">
         <v>17</v>
       </c>
       <c r="H41" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="I41" t="s">
         <v>53</v>
@@ -5608,39 +5608,39 @@
         <v>20</v>
       </c>
       <c r="K41" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M41" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>440</v>
+      </c>
+      <c r="B42" t="s">
         <v>441</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>442</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>443</v>
-      </c>
-      <c r="D42" t="s">
-        <v>444</v>
       </c>
       <c r="E42" t="s">
         <v>35</v>
       </c>
       <c r="F42" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G42" t="s">
         <v>17</v>
       </c>
       <c r="H42" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I42" t="s">
         <v>53</v>
@@ -5649,109 +5649,109 @@
         <v>20</v>
       </c>
       <c r="K42" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M42" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>827</v>
+      </c>
+      <c r="B43" t="s">
         <v>828</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>829</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>830</v>
       </c>
-      <c r="D43" t="s">
+      <c r="F43" t="s">
         <v>831</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>832</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" t="s">
         <v>833</v>
-      </c>
-      <c r="H43" t="s">
-        <v>834</v>
       </c>
       <c r="I43" t="s">
         <v>19</v>
       </c>
       <c r="K43" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M43" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>346</v>
+      </c>
+      <c r="B44" t="s">
         <v>347</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>348</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>349</v>
-      </c>
-      <c r="D44" t="s">
-        <v>350</v>
       </c>
       <c r="E44" t="s">
         <v>35</v>
       </c>
       <c r="F44" t="s">
+        <v>350</v>
+      </c>
+      <c r="G44" t="s">
         <v>351</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>352</v>
-      </c>
-      <c r="H44" t="s">
-        <v>353</v>
       </c>
       <c r="I44" t="s">
         <v>53</v>
       </c>
       <c r="K44" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M44" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>664</v>
+      </c>
+      <c r="B45" t="s">
         <v>665</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>666</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>667</v>
       </c>
-      <c r="D45" t="s">
+      <c r="F45" t="s">
         <v>668</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>669</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>670</v>
-      </c>
-      <c r="H45" t="s">
-        <v>671</v>
       </c>
       <c r="I45" t="s">
         <v>19</v>
@@ -5760,36 +5760,36 @@
         <v>61</v>
       </c>
       <c r="K45" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M45" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>672</v>
+      </c>
+      <c r="B46" t="s">
         <v>673</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>674</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>675</v>
       </c>
-      <c r="D46" t="s">
+      <c r="F46" t="s">
         <v>676</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>677</v>
       </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
         <v>678</v>
-      </c>
-      <c r="H46" t="s">
-        <v>679</v>
       </c>
       <c r="I46" t="s">
         <v>19</v>
@@ -5798,74 +5798,74 @@
         <v>61</v>
       </c>
       <c r="K46" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M46" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>680</v>
+      </c>
+      <c r="B47" t="s">
         <v>681</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>682</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>683</v>
       </c>
-      <c r="D47" t="s">
+      <c r="F47" t="s">
         <v>684</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
+        <v>262</v>
+      </c>
+      <c r="H47" t="s">
         <v>685</v>
       </c>
-      <c r="G47" t="s">
-        <v>263</v>
-      </c>
-      <c r="H47" t="s">
-        <v>686</v>
-      </c>
       <c r="I47" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J47" t="s">
         <v>29</v>
       </c>
       <c r="K47" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M47" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>790</v>
+      </c>
+      <c r="B48" t="s">
         <v>791</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>792</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>793</v>
       </c>
-      <c r="D48" t="s">
+      <c r="F48" t="s">
         <v>794</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
+        <v>767</v>
+      </c>
+      <c r="H48" t="s">
         <v>795</v>
-      </c>
-      <c r="G48" t="s">
-        <v>768</v>
-      </c>
-      <c r="H48" t="s">
-        <v>796</v>
       </c>
       <c r="I48" t="s">
         <v>53</v>
@@ -5874,36 +5874,36 @@
         <v>61</v>
       </c>
       <c r="K48" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M48" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>797</v>
+      </c>
+      <c r="B49" t="s">
         <v>798</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>799</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>800</v>
       </c>
-      <c r="D49" t="s">
+      <c r="F49" t="s">
         <v>801</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
+        <v>351</v>
+      </c>
+      <c r="H49" t="s">
         <v>802</v>
-      </c>
-      <c r="G49" t="s">
-        <v>352</v>
-      </c>
-      <c r="H49" t="s">
-        <v>803</v>
       </c>
       <c r="I49" t="s">
         <v>19</v>
@@ -5912,36 +5912,36 @@
         <v>61</v>
       </c>
       <c r="K49" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M49" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>804</v>
+      </c>
+      <c r="B50" t="s">
         <v>805</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>806</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>807</v>
       </c>
-      <c r="D50" t="s">
+      <c r="F50" t="s">
         <v>808</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
+        <v>351</v>
+      </c>
+      <c r="H50" t="s">
         <v>809</v>
-      </c>
-      <c r="G50" t="s">
-        <v>352</v>
-      </c>
-      <c r="H50" t="s">
-        <v>810</v>
       </c>
       <c r="I50" t="s">
         <v>19</v>
@@ -5950,71 +5950,71 @@
         <v>61</v>
       </c>
       <c r="K50" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="M50" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>265</v>
+      </c>
+      <c r="B51" t="s">
         <v>266</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>267</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>268</v>
       </c>
-      <c r="D51" t="s">
+      <c r="F51" t="s">
         <v>269</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>270</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
         <v>271</v>
-      </c>
-      <c r="H51" t="s">
-        <v>272</v>
       </c>
       <c r="I51" t="s">
         <v>53</v>
       </c>
       <c r="K51" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M51" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>273</v>
+      </c>
+      <c r="B52" t="s">
         <v>274</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>275</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>276</v>
       </c>
-      <c r="D52" t="s">
+      <c r="F52" t="s">
         <v>277</v>
       </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>278</v>
       </c>
-      <c r="G52" t="s">
+      <c r="H52" t="s">
         <v>279</v>
-      </c>
-      <c r="H52" t="s">
-        <v>280</v>
       </c>
       <c r="I52" t="s">
         <v>53</v>
@@ -6023,36 +6023,36 @@
         <v>61</v>
       </c>
       <c r="K52" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M52" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>281</v>
+      </c>
+      <c r="B53" t="s">
         <v>282</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>283</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
         <v>284</v>
       </c>
-      <c r="D53" t="s">
+      <c r="F53" t="s">
+        <v>277</v>
+      </c>
+      <c r="G53" t="s">
         <v>285</v>
       </c>
-      <c r="F53" t="s">
-        <v>278</v>
-      </c>
-      <c r="G53" t="s">
+      <c r="H53" t="s">
         <v>286</v>
-      </c>
-      <c r="H53" t="s">
-        <v>287</v>
       </c>
       <c r="I53" t="s">
         <v>53</v>
@@ -6061,36 +6061,36 @@
         <v>61</v>
       </c>
       <c r="K53" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="M53" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>181</v>
+      </c>
+      <c r="B54" t="s">
         <v>182</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>183</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>184</v>
       </c>
-      <c r="D54" t="s">
+      <c r="F54" t="s">
         <v>185</v>
       </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>186</v>
       </c>
-      <c r="G54" t="s">
+      <c r="H54" t="s">
         <v>187</v>
-      </c>
-      <c r="H54" t="s">
-        <v>188</v>
       </c>
       <c r="I54" t="s">
         <v>19</v>
@@ -6099,36 +6099,36 @@
         <v>61</v>
       </c>
       <c r="K54" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="M54" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>482</v>
+      </c>
+      <c r="B55" t="s">
         <v>483</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>484</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>485</v>
       </c>
-      <c r="D55" t="s">
+      <c r="F55" t="s">
         <v>486</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>487</v>
       </c>
-      <c r="G55" t="s">
+      <c r="H55" t="s">
         <v>488</v>
-      </c>
-      <c r="H55" t="s">
-        <v>489</v>
       </c>
       <c r="I55" t="s">
         <v>19</v>
@@ -6137,74 +6137,74 @@
         <v>61</v>
       </c>
       <c r="K55" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="M55" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>490</v>
+      </c>
+      <c r="B56" t="s">
         <v>491</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>492</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>493</v>
       </c>
-      <c r="D56" t="s">
+      <c r="F56" t="s">
         <v>494</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>495</v>
       </c>
-      <c r="G56" t="s">
+      <c r="H56" t="s">
         <v>496</v>
       </c>
-      <c r="H56" t="s">
-        <v>497</v>
-      </c>
       <c r="I56" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J56" t="s">
         <v>61</v>
       </c>
       <c r="K56" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="M56" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>513</v>
+      </c>
+      <c r="B57" t="s">
         <v>514</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>515</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>516</v>
       </c>
-      <c r="D57" t="s">
+      <c r="F57" t="s">
         <v>517</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>518</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
         <v>519</v>
-      </c>
-      <c r="H57" t="s">
-        <v>520</v>
       </c>
       <c r="I57" t="s">
         <v>53</v>
@@ -6213,112 +6213,112 @@
         <v>61</v>
       </c>
       <c r="K57" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="M57" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>528</v>
+      </c>
+      <c r="B58" t="s">
         <v>529</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>530</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>531</v>
       </c>
-      <c r="D58" t="s">
+      <c r="F58" t="s">
         <v>532</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>533</v>
       </c>
-      <c r="G58" t="s">
+      <c r="H58" t="s">
         <v>534</v>
       </c>
-      <c r="H58" t="s">
+      <c r="I58" t="s">
         <v>535</v>
-      </c>
-      <c r="I58" t="s">
-        <v>536</v>
       </c>
       <c r="J58" t="s">
         <v>29</v>
       </c>
       <c r="K58" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="M58" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>521</v>
+      </c>
+      <c r="B59" t="s">
         <v>522</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>523</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>524</v>
       </c>
-      <c r="D59" t="s">
+      <c r="F59" t="s">
         <v>525</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>526</v>
       </c>
-      <c r="G59" t="s">
+      <c r="H59" t="s">
         <v>527</v>
       </c>
-      <c r="H59" t="s">
-        <v>528</v>
-      </c>
       <c r="I59" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J59" t="s">
         <v>61</v>
       </c>
       <c r="K59" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="M59" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>536</v>
+      </c>
+      <c r="B60" t="s">
         <v>537</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>538</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
         <v>539</v>
       </c>
-      <c r="D60" t="s">
+      <c r="F60" t="s">
         <v>540</v>
       </c>
-      <c r="F60" t="s">
+      <c r="G60" t="s">
         <v>541</v>
       </c>
-      <c r="G60" t="s">
+      <c r="H60" t="s">
         <v>542</v>
-      </c>
-      <c r="H60" t="s">
-        <v>543</v>
       </c>
       <c r="I60" t="s">
         <v>19</v>
@@ -6327,51 +6327,51 @@
         <v>61</v>
       </c>
       <c r="K60" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="M60" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>544</v>
+      </c>
+      <c r="B61" t="s">
         <v>545</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>546</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>547</v>
       </c>
-      <c r="D61" t="s">
+      <c r="F61" t="s">
         <v>548</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>549</v>
       </c>
-      <c r="G61" t="s">
+      <c r="H61" t="s">
         <v>550</v>
       </c>
-      <c r="H61" t="s">
+      <c r="I61" t="s">
         <v>551</v>
-      </c>
-      <c r="I61" t="s">
-        <v>552</v>
       </c>
       <c r="J61" t="s">
         <v>61</v>
       </c>
       <c r="K61" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="M61" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.3">
@@ -6409,10 +6409,10 @@
         <v>71</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M62" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
@@ -6450,10 +6450,10 @@
         <v>79</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M63" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.3">
@@ -6491,10 +6491,10 @@
         <v>88</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M64" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
@@ -6532,36 +6532,36 @@
         <v>97</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M65" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
+        <v>360</v>
+      </c>
+      <c r="B66" t="s">
         <v>361</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
         <v>362</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>363</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>364</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>365</v>
-      </c>
-      <c r="F66" t="s">
-        <v>366</v>
       </c>
       <c r="G66" t="s">
         <v>17</v>
       </c>
       <c r="H66" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I66" t="s">
         <v>19</v>
@@ -6570,39 +6570,39 @@
         <v>87</v>
       </c>
       <c r="K66" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M66" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
+        <v>376</v>
+      </c>
+      <c r="B67" t="s">
         <v>377</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
         <v>378</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
         <v>379</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>380</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>381</v>
-      </c>
-      <c r="F67" t="s">
-        <v>382</v>
       </c>
       <c r="G67" t="s">
         <v>17</v>
       </c>
       <c r="H67" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I67" t="s">
         <v>19</v>
@@ -6611,80 +6611,80 @@
         <v>20</v>
       </c>
       <c r="K67" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M67" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>384</v>
+      </c>
+      <c r="B68" t="s">
         <v>385</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>386</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
         <v>387</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>388</v>
       </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
         <v>389</v>
-      </c>
-      <c r="F68" t="s">
-        <v>390</v>
       </c>
       <c r="G68" t="s">
         <v>17</v>
       </c>
       <c r="H68" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I68" t="s">
         <v>19</v>
       </c>
       <c r="J68" t="s">
+        <v>391</v>
+      </c>
+      <c r="K68" t="s">
         <v>392</v>
       </c>
-      <c r="K68" t="s">
-        <v>393</v>
-      </c>
       <c r="L68" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M68" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>393</v>
+      </c>
+      <c r="B69" t="s">
         <v>394</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>395</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
         <v>396</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>397</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>398</v>
-      </c>
-      <c r="F69" t="s">
-        <v>399</v>
       </c>
       <c r="G69" t="s">
         <v>17</v>
       </c>
       <c r="H69" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I69" t="s">
         <v>19</v>
@@ -6693,191 +6693,191 @@
         <v>87</v>
       </c>
       <c r="K69" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M69" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>447</v>
+      </c>
+      <c r="B70" t="s">
         <v>448</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>449</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
         <v>450</v>
       </c>
-      <c r="D70" t="s">
+      <c r="F70" t="s">
         <v>451</v>
-      </c>
-      <c r="F70" t="s">
-        <v>452</v>
       </c>
       <c r="G70" t="s">
         <v>17</v>
       </c>
       <c r="H70" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I70" t="s">
         <v>19</v>
       </c>
       <c r="J70" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K70" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M70" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>454</v>
+      </c>
+      <c r="B71" t="s">
         <v>455</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>456</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
         <v>457</v>
       </c>
-      <c r="D71" t="s">
+      <c r="F71" t="s">
         <v>458</v>
-      </c>
-      <c r="F71" t="s">
-        <v>459</v>
       </c>
       <c r="G71" t="s">
         <v>17</v>
       </c>
       <c r="H71" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I71" t="s">
         <v>19</v>
       </c>
       <c r="J71" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K71" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M71" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>475</v>
+      </c>
+      <c r="B72" t="s">
         <v>476</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>477</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
         <v>478</v>
       </c>
-      <c r="D72" t="s">
+      <c r="F72" t="s">
         <v>479</v>
-      </c>
-      <c r="F72" t="s">
-        <v>480</v>
       </c>
       <c r="G72" t="s">
         <v>17</v>
       </c>
       <c r="H72" t="s">
+        <v>480</v>
+      </c>
+      <c r="I72" t="s">
         <v>481</v>
       </c>
-      <c r="I72" t="s">
-        <v>482</v>
-      </c>
       <c r="J72" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K72" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M72" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>687</v>
+      </c>
+      <c r="B73" t="s">
         <v>688</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
         <v>689</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D73" t="s">
         <v>690</v>
       </c>
-      <c r="D73" t="s">
+      <c r="F73" t="s">
         <v>691</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
         <v>692</v>
       </c>
-      <c r="G73" t="s">
+      <c r="H73" t="s">
         <v>693</v>
       </c>
-      <c r="H73" t="s">
-        <v>694</v>
-      </c>
       <c r="I73" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J73" t="s">
         <v>61</v>
       </c>
       <c r="K73" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M73" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>778</v>
+      </c>
+      <c r="B74" t="s">
         <v>779</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
         <v>780</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
         <v>781</v>
-      </c>
-      <c r="D74" t="s">
-        <v>782</v>
       </c>
       <c r="E74" t="s">
         <v>15</v>
       </c>
       <c r="F74" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="G74" t="s">
         <v>17</v>
       </c>
       <c r="H74" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="I74" t="s">
         <v>19</v>
@@ -6889,33 +6889,33 @@
         <v>21</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M74" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>784</v>
+      </c>
+      <c r="B75" t="s">
         <v>785</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
         <v>786</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
         <v>787</v>
       </c>
-      <c r="D75" t="s">
+      <c r="F75" t="s">
         <v>788</v>
-      </c>
-      <c r="F75" t="s">
-        <v>789</v>
       </c>
       <c r="G75" t="s">
         <v>27</v>
       </c>
       <c r="H75" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="I75" t="s">
         <v>19</v>
@@ -6927,36 +6927,36 @@
         <v>30</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M75" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>811</v>
+      </c>
+      <c r="B76" t="s">
         <v>812</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>813</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>814</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>815</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>816</v>
-      </c>
-      <c r="F76" t="s">
-        <v>817</v>
       </c>
       <c r="G76" t="s">
         <v>17</v>
       </c>
       <c r="H76" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="I76" t="s">
         <v>19</v>
@@ -6965,40 +6965,40 @@
         <v>20</v>
       </c>
       <c r="K76" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="L76" s="1"/>
       <c r="M76" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="N76" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
+        <v>819</v>
+      </c>
+      <c r="B77" t="s">
         <v>820</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>821</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
         <v>822</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>823</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>824</v>
-      </c>
-      <c r="F77" t="s">
-        <v>825</v>
       </c>
       <c r="G77" t="s">
         <v>17</v>
       </c>
       <c r="H77" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="I77" t="s">
         <v>19</v>
@@ -7007,78 +7007,78 @@
         <v>20</v>
       </c>
       <c r="K77" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="L77" s="1"/>
       <c r="M77" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="N77" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>460</v>
+      </c>
+      <c r="B78" t="s">
         <v>461</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
         <v>462</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
         <v>463</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>464</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>465</v>
-      </c>
-      <c r="F78" t="s">
-        <v>466</v>
       </c>
       <c r="G78" t="s">
         <v>17</v>
       </c>
       <c r="H78" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="I78" t="s">
         <v>53</v>
       </c>
       <c r="K78" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="M78" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>468</v>
+      </c>
+      <c r="B79" t="s">
         <v>469</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
         <v>470</v>
       </c>
-      <c r="C79" t="s">
+      <c r="D79" t="s">
         <v>471</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
+        <v>464</v>
+      </c>
+      <c r="F79" t="s">
         <v>472</v>
-      </c>
-      <c r="E79" t="s">
-        <v>465</v>
-      </c>
-      <c r="F79" t="s">
-        <v>473</v>
       </c>
       <c r="G79" t="s">
         <v>17</v>
       </c>
       <c r="H79" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I79" t="s">
         <v>53</v>
@@ -7087,119 +7087,119 @@
         <v>87</v>
       </c>
       <c r="K79" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="M79" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>835</v>
+      </c>
+      <c r="B80" t="s">
         <v>836</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
         <v>837</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
         <v>838</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>839</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>840</v>
-      </c>
-      <c r="F80" t="s">
-        <v>841</v>
       </c>
       <c r="G80" t="s">
         <v>17</v>
       </c>
       <c r="H80" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="I80" t="s">
         <v>53</v>
       </c>
       <c r="K80" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="M80" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>850</v>
+      </c>
+      <c r="B81" t="s">
         <v>851</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>852</v>
       </c>
-      <c r="C81" t="s">
+      <c r="D81" t="s">
         <v>853</v>
-      </c>
-      <c r="D81" t="s">
-        <v>854</v>
       </c>
       <c r="E81" t="e">
         <f>-LOG(mol/l)</f>
         <v>#NAME?</v>
       </c>
       <c r="F81" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="G81" t="s">
         <v>17</v>
       </c>
       <c r="H81" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="I81" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J81" t="s">
         <v>20</v>
       </c>
       <c r="K81" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="M81" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
+        <v>401</v>
+      </c>
+      <c r="B82" t="s">
         <v>402</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>403</v>
       </c>
-      <c r="C82" t="s">
+      <c r="D82" t="s">
         <v>404</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
         <v>405</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>406</v>
-      </c>
-      <c r="F82" t="s">
-        <v>407</v>
       </c>
       <c r="G82" t="s">
         <v>17</v>
       </c>
       <c r="H82" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I82" t="s">
         <v>19</v>
@@ -7208,39 +7208,39 @@
         <v>87</v>
       </c>
       <c r="K82" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="M82" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
+        <v>581</v>
+      </c>
+      <c r="B83" t="s">
         <v>582</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>583</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
         <v>584</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
         <v>585</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>586</v>
-      </c>
-      <c r="F83" t="s">
-        <v>587</v>
       </c>
       <c r="G83" t="s">
         <v>17</v>
       </c>
       <c r="H83" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="I83" t="s">
         <v>19</v>
@@ -7249,39 +7249,39 @@
         <v>20</v>
       </c>
       <c r="K83" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="M83" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
+        <v>589</v>
+      </c>
+      <c r="B84" t="s">
         <v>590</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
         <v>591</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
         <v>592</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
+        <v>380</v>
+      </c>
+      <c r="F84" t="s">
         <v>593</v>
-      </c>
-      <c r="E84" t="s">
-        <v>381</v>
-      </c>
-      <c r="F84" t="s">
-        <v>594</v>
       </c>
       <c r="G84" t="s">
         <v>17</v>
       </c>
       <c r="H84" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="I84" t="s">
         <v>19</v>
@@ -7290,77 +7290,77 @@
         <v>20</v>
       </c>
       <c r="K84" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="M84" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
+        <v>596</v>
+      </c>
+      <c r="B85" t="s">
         <v>597</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>598</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
         <v>599</v>
       </c>
-      <c r="D85" t="s">
+      <c r="F85" t="s">
         <v>600</v>
       </c>
-      <c r="F85" t="s">
+      <c r="G85" t="s">
         <v>601</v>
       </c>
-      <c r="G85" t="s">
+      <c r="H85" t="s">
         <v>602</v>
-      </c>
-      <c r="H85" t="s">
-        <v>603</v>
       </c>
       <c r="I85" t="s">
         <v>19</v>
       </c>
       <c r="J85" t="s">
+        <v>603</v>
+      </c>
+      <c r="K85" t="s">
         <v>604</v>
       </c>
-      <c r="K85" t="s">
-        <v>605</v>
-      </c>
       <c r="L85" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="M85" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
+        <v>605</v>
+      </c>
+      <c r="B86" t="s">
         <v>606</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
         <v>607</v>
       </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
         <v>608</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
+        <v>380</v>
+      </c>
+      <c r="F86" t="s">
         <v>609</v>
-      </c>
-      <c r="E86" t="s">
-        <v>381</v>
-      </c>
-      <c r="F86" t="s">
-        <v>610</v>
       </c>
       <c r="G86" t="s">
         <v>17</v>
       </c>
       <c r="H86" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="I86" t="s">
         <v>19</v>
@@ -7369,77 +7369,77 @@
         <v>20</v>
       </c>
       <c r="K86" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="M86" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
+        <v>611</v>
+      </c>
+      <c r="B87" t="s">
         <v>612</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
         <v>613</v>
       </c>
-      <c r="C87" t="s">
+      <c r="D87" t="s">
         <v>614</v>
       </c>
-      <c r="D87" t="s">
+      <c r="F87" t="s">
         <v>615</v>
       </c>
-      <c r="F87" t="s">
+      <c r="G87" t="s">
+        <v>601</v>
+      </c>
+      <c r="H87" t="s">
         <v>616</v>
-      </c>
-      <c r="G87" t="s">
-        <v>602</v>
-      </c>
-      <c r="H87" t="s">
-        <v>617</v>
       </c>
       <c r="I87" t="s">
         <v>19</v>
       </c>
       <c r="J87" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="K87" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="M87" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
+        <v>618</v>
+      </c>
+      <c r="B88" t="s">
         <v>619</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>620</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D88" t="s">
         <v>621</v>
       </c>
-      <c r="D88" t="s">
+      <c r="E88" t="s">
+        <v>380</v>
+      </c>
+      <c r="F88" t="s">
         <v>622</v>
-      </c>
-      <c r="E88" t="s">
-        <v>381</v>
-      </c>
-      <c r="F88" t="s">
-        <v>623</v>
       </c>
       <c r="G88" t="s">
         <v>17</v>
       </c>
       <c r="H88" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="I88" t="s">
         <v>19</v>
@@ -7448,220 +7448,220 @@
         <v>20</v>
       </c>
       <c r="K88" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="M88" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>624</v>
+      </c>
+      <c r="B89" t="s">
         <v>625</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
         <v>626</v>
       </c>
-      <c r="C89" t="s">
+      <c r="D89" t="s">
         <v>627</v>
       </c>
-      <c r="D89" t="s">
+      <c r="F89" t="s">
         <v>628</v>
       </c>
-      <c r="F89" t="s">
+      <c r="G89" t="s">
+        <v>601</v>
+      </c>
+      <c r="H89" t="s">
         <v>629</v>
-      </c>
-      <c r="G89" t="s">
-        <v>602</v>
-      </c>
-      <c r="H89" t="s">
-        <v>630</v>
       </c>
       <c r="I89" t="s">
         <v>19</v>
       </c>
       <c r="J89" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="K89" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="M89" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
+        <v>232</v>
+      </c>
+      <c r="B90" t="s">
         <v>233</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
         <v>234</v>
       </c>
-      <c r="C90" t="s">
+      <c r="D90" t="s">
         <v>235</v>
       </c>
-      <c r="D90" t="s">
+      <c r="F90" t="s">
         <v>236</v>
       </c>
-      <c r="F90" t="s">
+      <c r="G90" t="s">
         <v>237</v>
       </c>
-      <c r="G90" t="s">
+      <c r="H90" t="s">
         <v>238</v>
       </c>
-      <c r="H90" t="s">
+      <c r="I90" t="s">
         <v>239</v>
-      </c>
-      <c r="I90" t="s">
-        <v>240</v>
       </c>
       <c r="J90" t="s">
         <v>29</v>
       </c>
       <c r="K90" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="M90" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
+        <v>241</v>
+      </c>
+      <c r="B91" t="s">
         <v>242</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
         <v>243</v>
       </c>
-      <c r="C91" t="s">
+      <c r="D91" t="s">
         <v>244</v>
       </c>
-      <c r="D91" t="s">
+      <c r="F91" t="s">
         <v>245</v>
       </c>
-      <c r="F91" t="s">
+      <c r="G91" t="s">
         <v>246</v>
       </c>
-      <c r="G91" t="s">
+      <c r="H91" t="s">
         <v>247</v>
       </c>
-      <c r="H91" t="s">
+      <c r="I91" t="s">
         <v>248</v>
-      </c>
-      <c r="I91" t="s">
-        <v>249</v>
       </c>
       <c r="J91" t="s">
         <v>61</v>
       </c>
       <c r="K91" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="M91" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
+        <v>257</v>
+      </c>
+      <c r="B92" t="s">
         <v>258</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>259</v>
       </c>
-      <c r="C92" t="s">
+      <c r="D92" t="s">
         <v>260</v>
       </c>
-      <c r="D92" t="s">
+      <c r="F92" t="s">
         <v>261</v>
       </c>
-      <c r="F92" t="s">
+      <c r="G92" t="s">
         <v>262</v>
       </c>
-      <c r="G92" t="s">
+      <c r="H92" t="s">
         <v>263</v>
-      </c>
-      <c r="H92" t="s">
-        <v>264</v>
       </c>
       <c r="I92" t="s">
         <v>53</v>
       </c>
       <c r="K92" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="M92" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
+        <v>718</v>
+      </c>
+      <c r="B93" t="s">
         <v>719</v>
       </c>
-      <c r="B93" t="s">
+      <c r="C93" t="s">
         <v>720</v>
       </c>
-      <c r="C93" t="s">
+      <c r="D93" t="s">
         <v>721</v>
       </c>
-      <c r="D93" t="s">
+      <c r="F93" t="s">
         <v>722</v>
       </c>
-      <c r="F93" t="s">
+      <c r="G93" t="s">
+        <v>700</v>
+      </c>
+      <c r="H93" t="s">
         <v>723</v>
-      </c>
-      <c r="G93" t="s">
-        <v>701</v>
-      </c>
-      <c r="H93" t="s">
-        <v>724</v>
       </c>
       <c r="I93" t="s">
         <v>53</v>
       </c>
       <c r="K93" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M93" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
+        <v>725</v>
+      </c>
+      <c r="B94" t="s">
         <v>726</v>
       </c>
-      <c r="B94" t="s">
+      <c r="C94" t="s">
         <v>727</v>
       </c>
-      <c r="C94" t="s">
+      <c r="D94" t="s">
         <v>728</v>
       </c>
-      <c r="D94" t="s">
+      <c r="F94" t="s">
         <v>729</v>
       </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
         <v>730</v>
       </c>
-      <c r="G94" t="s">
+      <c r="H94" t="s">
         <v>731</v>
-      </c>
-      <c r="H94" t="s">
-        <v>732</v>
       </c>
       <c r="I94" t="s">
         <v>53</v>
@@ -7670,36 +7670,36 @@
         <v>61</v>
       </c>
       <c r="K94" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M94" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
+        <v>733</v>
+      </c>
+      <c r="B95" t="s">
         <v>734</v>
       </c>
-      <c r="B95" t="s">
+      <c r="C95" t="s">
         <v>735</v>
       </c>
-      <c r="C95" t="s">
+      <c r="D95" t="s">
         <v>736</v>
       </c>
-      <c r="D95" t="s">
+      <c r="F95" t="s">
         <v>737</v>
       </c>
-      <c r="F95" t="s">
+      <c r="G95" t="s">
+        <v>285</v>
+      </c>
+      <c r="H95" t="s">
         <v>738</v>
-      </c>
-      <c r="G95" t="s">
-        <v>286</v>
-      </c>
-      <c r="H95" t="s">
-        <v>739</v>
       </c>
       <c r="I95" t="s">
         <v>53</v>
@@ -7708,74 +7708,74 @@
         <v>61</v>
       </c>
       <c r="K95" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M95" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
+        <v>695</v>
+      </c>
+      <c r="B96" t="s">
         <v>696</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C96" t="s">
         <v>697</v>
       </c>
-      <c r="C96" t="s">
+      <c r="D96" t="s">
         <v>698</v>
       </c>
-      <c r="D96" t="s">
+      <c r="F96" t="s">
         <v>699</v>
       </c>
-      <c r="F96" t="s">
+      <c r="G96" t="s">
         <v>700</v>
       </c>
-      <c r="G96" t="s">
+      <c r="H96" t="s">
         <v>701</v>
       </c>
-      <c r="H96" t="s">
+      <c r="I96" t="s">
         <v>702</v>
-      </c>
-      <c r="I96" t="s">
-        <v>703</v>
       </c>
       <c r="J96" t="s">
         <v>29</v>
       </c>
       <c r="K96" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="M96" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
+        <v>711</v>
+      </c>
+      <c r="B97" t="s">
         <v>712</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
         <v>713</v>
       </c>
-      <c r="C97" t="s">
+      <c r="D97" t="s">
         <v>714</v>
       </c>
-      <c r="D97" t="s">
+      <c r="F97" t="s">
         <v>715</v>
       </c>
-      <c r="F97" t="s">
+      <c r="G97" t="s">
+        <v>700</v>
+      </c>
+      <c r="H97" t="s">
         <v>716</v>
-      </c>
-      <c r="G97" t="s">
-        <v>701</v>
-      </c>
-      <c r="H97" t="s">
-        <v>717</v>
       </c>
       <c r="I97" t="s">
         <v>19</v>
@@ -7784,36 +7784,36 @@
         <v>29</v>
       </c>
       <c r="K97" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="L97" s="4" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="M97" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
+        <v>704</v>
+      </c>
+      <c r="B98" t="s">
         <v>705</v>
       </c>
-      <c r="B98" t="s">
+      <c r="C98" t="s">
         <v>706</v>
       </c>
-      <c r="C98" t="s">
+      <c r="D98" t="s">
         <v>707</v>
       </c>
-      <c r="D98" t="s">
+      <c r="F98" t="s">
         <v>708</v>
       </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
+        <v>700</v>
+      </c>
+      <c r="H98" t="s">
         <v>709</v>
-      </c>
-      <c r="G98" t="s">
-        <v>701</v>
-      </c>
-      <c r="H98" t="s">
-        <v>710</v>
       </c>
       <c r="I98" t="s">
         <v>19</v>
@@ -7822,71 +7822,71 @@
         <v>29</v>
       </c>
       <c r="K98" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="L98" s="4" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="M98" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
+        <v>754</v>
+      </c>
+      <c r="B99" t="s">
         <v>755</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
         <v>756</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
         <v>757</v>
       </c>
-      <c r="D99" t="s">
+      <c r="F99" t="s">
         <v>758</v>
       </c>
-      <c r="F99" t="s">
+      <c r="G99" t="s">
         <v>759</v>
       </c>
-      <c r="G99" t="s">
+      <c r="H99" t="s">
         <v>760</v>
-      </c>
-      <c r="H99" t="s">
-        <v>761</v>
       </c>
       <c r="I99" t="s">
         <v>53</v>
       </c>
       <c r="K99" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="L99" s="4" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="M99" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
+        <v>762</v>
+      </c>
+      <c r="B100" t="s">
         <v>763</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C100" t="s">
         <v>764</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
         <v>765</v>
       </c>
-      <c r="D100" t="s">
+      <c r="F100" t="s">
         <v>766</v>
       </c>
-      <c r="F100" t="s">
+      <c r="G100" t="s">
         <v>767</v>
       </c>
-      <c r="G100" t="s">
+      <c r="H100" t="s">
         <v>768</v>
-      </c>
-      <c r="H100" t="s">
-        <v>769</v>
       </c>
       <c r="I100" t="s">
         <v>53</v>
@@ -7895,74 +7895,74 @@
         <v>61</v>
       </c>
       <c r="K100" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L100" s="4" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="M100" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
+        <v>770</v>
+      </c>
+      <c r="B101" t="s">
         <v>771</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C101" t="s">
         <v>772</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D101" t="s">
         <v>773</v>
       </c>
-      <c r="D101" t="s">
+      <c r="F101" t="s">
         <v>774</v>
       </c>
-      <c r="F101" t="s">
+      <c r="G101" t="s">
         <v>775</v>
       </c>
-      <c r="G101" t="s">
+      <c r="H101" t="s">
         <v>776</v>
-      </c>
-      <c r="H101" t="s">
-        <v>777</v>
       </c>
       <c r="I101" t="s">
         <v>53</v>
       </c>
       <c r="K101" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="M101" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
+        <v>425</v>
+      </c>
+      <c r="B102" t="s">
         <v>426</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" t="s">
         <v>427</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
         <v>428</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
+        <v>421</v>
+      </c>
+      <c r="F102" t="s">
         <v>429</v>
-      </c>
-      <c r="E102" t="s">
-        <v>422</v>
-      </c>
-      <c r="F102" t="s">
-        <v>430</v>
       </c>
       <c r="G102" t="s">
         <v>17</v>
       </c>
       <c r="H102" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I102" t="s">
         <v>53</v>
@@ -7971,39 +7971,39 @@
         <v>20</v>
       </c>
       <c r="K102" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="M102" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
+        <v>432</v>
+      </c>
+      <c r="B103" t="s">
         <v>433</v>
       </c>
-      <c r="B103" t="s">
+      <c r="C103" t="s">
         <v>434</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
         <v>435</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
         <v>436</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>437</v>
-      </c>
-      <c r="F103" t="s">
-        <v>438</v>
       </c>
       <c r="G103" t="s">
         <v>17</v>
       </c>
       <c r="H103" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I103" t="s">
         <v>19</v>
@@ -8012,80 +8012,80 @@
         <v>87</v>
       </c>
       <c r="K103" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="M103" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
+        <v>417</v>
+      </c>
+      <c r="B104" t="s">
         <v>418</v>
       </c>
-      <c r="B104" t="s">
+      <c r="C104" t="s">
         <v>419</v>
       </c>
-      <c r="C104" t="s">
+      <c r="D104" t="s">
         <v>420</v>
       </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
         <v>421</v>
       </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
         <v>422</v>
-      </c>
-      <c r="F104" t="s">
-        <v>423</v>
       </c>
       <c r="G104" t="s">
         <v>17</v>
       </c>
       <c r="H104" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I104" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J104" t="s">
         <v>20</v>
       </c>
       <c r="K104" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="M104" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
+        <v>560</v>
+      </c>
+      <c r="B105" t="s">
         <v>561</v>
       </c>
-      <c r="B105" t="s">
+      <c r="C105" t="s">
         <v>562</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105" t="s">
         <v>563</v>
       </c>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
+        <v>421</v>
+      </c>
+      <c r="F105" t="s">
         <v>564</v>
-      </c>
-      <c r="E105" t="s">
-        <v>422</v>
-      </c>
-      <c r="F105" t="s">
-        <v>565</v>
       </c>
       <c r="G105" t="s">
         <v>17</v>
       </c>
       <c r="H105" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="I105" t="s">
         <v>53</v>
@@ -8094,40 +8094,40 @@
         <v>20</v>
       </c>
       <c r="K105" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="M105" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
+        <v>567</v>
+      </c>
+      <c r="B106" t="s">
         <v>568</v>
       </c>
-      <c r="B106" t="s">
+      <c r="C106" t="s">
         <v>569</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
         <v>570</v>
-      </c>
-      <c r="D106" t="s">
-        <v>571</v>
       </c>
       <c r="E106" t="e">
         <f>-LOG(mg/kg)</f>
         <v>#NAME?</v>
       </c>
       <c r="F106" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G106" t="s">
         <v>17</v>
       </c>
       <c r="H106" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I106" t="s">
         <v>19</v>
@@ -8136,112 +8136,112 @@
         <v>20</v>
       </c>
       <c r="K106" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="M106" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
+        <v>553</v>
+      </c>
+      <c r="B107" t="s">
         <v>554</v>
       </c>
-      <c r="B107" t="s">
+      <c r="C107" t="s">
         <v>555</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
         <v>556</v>
       </c>
-      <c r="D107" t="s">
+      <c r="E107" t="s">
+        <v>421</v>
+      </c>
+      <c r="F107" t="s">
         <v>557</v>
-      </c>
-      <c r="E107" t="s">
-        <v>422</v>
-      </c>
-      <c r="F107" t="s">
-        <v>558</v>
       </c>
       <c r="G107" t="s">
         <v>17</v>
       </c>
       <c r="H107" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="I107" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J107" t="s">
         <v>20</v>
       </c>
       <c r="K107" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="M107" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
+        <v>189</v>
+      </c>
+      <c r="B108" t="s">
         <v>190</v>
       </c>
-      <c r="B108" t="s">
+      <c r="C108" t="s">
         <v>191</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
         <v>192</v>
       </c>
-      <c r="D108" t="s">
+      <c r="F108" t="s">
         <v>193</v>
-      </c>
-      <c r="F108" t="s">
-        <v>194</v>
       </c>
       <c r="G108" t="s">
         <v>17</v>
       </c>
       <c r="H108" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I108" t="s">
         <v>19</v>
       </c>
       <c r="K108" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="M108" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
+        <v>368</v>
+      </c>
+      <c r="B109" t="s">
         <v>369</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C109" t="s">
         <v>370</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
         <v>371</v>
       </c>
-      <c r="D109" t="s">
+      <c r="F109" t="s">
         <v>372</v>
       </c>
-      <c r="F109" t="s">
+      <c r="G109" t="s">
         <v>373</v>
       </c>
-      <c r="G109" t="s">
+      <c r="H109" t="s">
         <v>374</v>
-      </c>
-      <c r="H109" t="s">
-        <v>375</v>
       </c>
       <c r="I109" t="s">
         <v>19</v>
@@ -8250,39 +8250,39 @@
         <v>61</v>
       </c>
       <c r="K109" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="M109" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
+        <v>409</v>
+      </c>
+      <c r="B110" t="s">
         <v>410</v>
       </c>
-      <c r="B110" t="s">
+      <c r="C110" t="s">
         <v>411</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
         <v>412</v>
       </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
         <v>413</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
         <v>414</v>
-      </c>
-      <c r="F110" t="s">
-        <v>415</v>
       </c>
       <c r="G110" t="s">
         <v>17</v>
       </c>
       <c r="H110" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I110" t="s">
         <v>53</v>
@@ -8291,39 +8291,39 @@
         <v>87</v>
       </c>
       <c r="K110" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="M110" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
+        <v>740</v>
+      </c>
+      <c r="B111" t="s">
         <v>741</v>
       </c>
-      <c r="B111" t="s">
+      <c r="C111" t="s">
         <v>742</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
         <v>743</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
         <v>744</v>
       </c>
-      <c r="E111" t="s">
+      <c r="F111" t="s">
         <v>745</v>
-      </c>
-      <c r="F111" t="s">
-        <v>746</v>
       </c>
       <c r="G111" t="s">
         <v>17</v>
       </c>
       <c r="H111" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="I111" t="s">
         <v>19</v>
@@ -8332,42 +8332,42 @@
         <v>20</v>
       </c>
       <c r="K111" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="M111" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="N111" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
+        <v>748</v>
+      </c>
+      <c r="B112" t="s">
         <v>749</v>
       </c>
-      <c r="B112" t="s">
+      <c r="C112" t="s">
         <v>750</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
         <v>751</v>
       </c>
-      <c r="D112" t="s">
+      <c r="E112" t="s">
+        <v>744</v>
+      </c>
+      <c r="F112" t="s">
         <v>752</v>
-      </c>
-      <c r="E112" t="s">
-        <v>745</v>
-      </c>
-      <c r="F112" t="s">
-        <v>753</v>
       </c>
       <c r="G112" t="s">
         <v>17</v>
       </c>
       <c r="H112" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="I112" t="s">
         <v>19</v>
@@ -8376,16 +8376,16 @@
         <v>20</v>
       </c>
       <c r="K112" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="M112" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="N112" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.3">
@@ -8405,10 +8405,10 @@
         <v>102</v>
       </c>
       <c r="G113" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H113" t="s">
         <v>103</v>
-      </c>
-      <c r="H113" t="s">
-        <v>104</v>
       </c>
       <c r="I113" t="s">
         <v>19</v>
@@ -8417,58 +8417,58 @@
         <v>61</v>
       </c>
       <c r="K113" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="M113" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="N113" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
+        <v>250</v>
+      </c>
+      <c r="B114" t="s">
         <v>251</v>
       </c>
-      <c r="B114" t="s">
+      <c r="C114" t="s">
         <v>252</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
         <v>253</v>
-      </c>
-      <c r="D114" t="s">
-        <v>254</v>
       </c>
       <c r="E114" t="e">
         <f>-Log mg/kg</f>
         <v>#NAME?</v>
       </c>
       <c r="F114" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G114" t="s">
         <v>17</v>
       </c>
       <c r="H114" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I114" t="s">
         <v>53</v>
       </c>
       <c r="K114" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="M114" t="s">
+        <v>1002</v>
+      </c>
+      <c r="N114" t="s">
         <v>1003</v>
-      </c>
-      <c r="N114" t="s">
-        <v>1004</v>
       </c>
     </row>
   </sheetData>
@@ -8490,458 +8490,458 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>994</v>
+      </c>
+      <c r="B1" t="s">
         <v>995</v>
-      </c>
-      <c r="B1" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>883</v>
+      </c>
+      <c r="B2" t="s">
         <v>884</v>
-      </c>
-      <c r="B2" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>885</v>
+      </c>
+      <c r="B3" t="s">
         <v>886</v>
-      </c>
-      <c r="B3" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>887</v>
+      </c>
+      <c r="B4" t="s">
         <v>888</v>
-      </c>
-      <c r="B4" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>889</v>
+      </c>
+      <c r="B5" t="s">
         <v>890</v>
-      </c>
-      <c r="B5" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>891</v>
+      </c>
+      <c r="B6" t="s">
         <v>892</v>
-      </c>
-      <c r="B6" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>893</v>
+      </c>
+      <c r="B7" t="s">
         <v>894</v>
-      </c>
-      <c r="B7" t="s">
-        <v>895</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>895</v>
+      </c>
+      <c r="B8" t="s">
         <v>896</v>
-      </c>
-      <c r="B8" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>897</v>
+      </c>
+      <c r="B9" t="s">
         <v>898</v>
-      </c>
-      <c r="B9" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>899</v>
+      </c>
+      <c r="B10" t="s">
         <v>900</v>
-      </c>
-      <c r="B10" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>901</v>
+      </c>
+      <c r="B11" t="s">
         <v>902</v>
-      </c>
-      <c r="B11" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>903</v>
+      </c>
+      <c r="B12" t="s">
         <v>904</v>
-      </c>
-      <c r="B12" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>905</v>
+      </c>
+      <c r="B13" t="s">
         <v>906</v>
-      </c>
-      <c r="B13" t="s">
-        <v>907</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>907</v>
+      </c>
+      <c r="B14" t="s">
         <v>908</v>
-      </c>
-      <c r="B14" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>909</v>
+      </c>
+      <c r="B15" t="s">
         <v>910</v>
-      </c>
-      <c r="B15" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>911</v>
+      </c>
+      <c r="B16" t="s">
         <v>912</v>
-      </c>
-      <c r="B16" t="s">
-        <v>913</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>913</v>
+      </c>
+      <c r="B17" t="s">
         <v>914</v>
-      </c>
-      <c r="B17" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>915</v>
+      </c>
+      <c r="B18" t="s">
         <v>916</v>
-      </c>
-      <c r="B18" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>917</v>
+      </c>
+      <c r="B19" t="s">
         <v>918</v>
-      </c>
-      <c r="B19" t="s">
-        <v>919</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>919</v>
+      </c>
+      <c r="B20" t="s">
         <v>920</v>
-      </c>
-      <c r="B20" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>921</v>
+      </c>
+      <c r="B21" t="s">
         <v>922</v>
-      </c>
-      <c r="B21" t="s">
-        <v>923</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>923</v>
+      </c>
+      <c r="B22" t="s">
         <v>924</v>
-      </c>
-      <c r="B22" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>925</v>
+      </c>
+      <c r="B23" t="s">
         <v>926</v>
-      </c>
-      <c r="B23" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>927</v>
+      </c>
+      <c r="B24" t="s">
         <v>928</v>
-      </c>
-      <c r="B24" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>929</v>
+      </c>
+      <c r="B25" t="s">
         <v>930</v>
-      </c>
-      <c r="B25" t="s">
-        <v>931</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>931</v>
+      </c>
+      <c r="B26" t="s">
         <v>932</v>
-      </c>
-      <c r="B26" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>933</v>
+      </c>
+      <c r="B27" t="s">
         <v>934</v>
-      </c>
-      <c r="B27" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>935</v>
+      </c>
+      <c r="B28" t="s">
         <v>936</v>
-      </c>
-      <c r="B28" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>937</v>
+      </c>
+      <c r="B29" t="s">
         <v>938</v>
-      </c>
-      <c r="B29" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>939</v>
+      </c>
+      <c r="B30" t="s">
         <v>940</v>
-      </c>
-      <c r="B30" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>941</v>
+      </c>
+      <c r="B31" t="s">
         <v>942</v>
-      </c>
-      <c r="B31" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>943</v>
+      </c>
+      <c r="B32" t="s">
         <v>944</v>
-      </c>
-      <c r="B32" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>945</v>
+      </c>
+      <c r="B33" t="s">
         <v>946</v>
-      </c>
-      <c r="B33" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>947</v>
+      </c>
+      <c r="B34" t="s">
         <v>948</v>
-      </c>
-      <c r="B34" t="s">
-        <v>949</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>949</v>
+      </c>
+      <c r="B35" t="s">
         <v>950</v>
-      </c>
-      <c r="B35" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>951</v>
+      </c>
+      <c r="B36" t="s">
         <v>952</v>
-      </c>
-      <c r="B36" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>953</v>
+      </c>
+      <c r="B37" t="s">
         <v>954</v>
-      </c>
-      <c r="B37" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>955</v>
+      </c>
+      <c r="B38" t="s">
         <v>956</v>
-      </c>
-      <c r="B38" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>957</v>
+      </c>
+      <c r="B39" t="s">
         <v>958</v>
-      </c>
-      <c r="B39" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>959</v>
+      </c>
+      <c r="B40" t="s">
         <v>960</v>
-      </c>
-      <c r="B40" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>961</v>
+      </c>
+      <c r="B41" t="s">
         <v>962</v>
-      </c>
-      <c r="B41" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>963</v>
+      </c>
+      <c r="B42" t="s">
         <v>964</v>
-      </c>
-      <c r="B42" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>965</v>
+      </c>
+      <c r="B43" t="s">
         <v>966</v>
-      </c>
-      <c r="B43" t="s">
-        <v>967</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>967</v>
+      </c>
+      <c r="B44" t="s">
         <v>968</v>
-      </c>
-      <c r="B44" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>969</v>
+      </c>
+      <c r="B45" t="s">
         <v>970</v>
-      </c>
-      <c r="B45" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>971</v>
+      </c>
+      <c r="B46" t="s">
         <v>972</v>
-      </c>
-      <c r="B46" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>973</v>
+      </c>
+      <c r="B47" t="s">
         <v>974</v>
-      </c>
-      <c r="B47" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>975</v>
+      </c>
+      <c r="B48" t="s">
         <v>976</v>
-      </c>
-      <c r="B48" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>977</v>
+      </c>
+      <c r="B49" t="s">
         <v>978</v>
-      </c>
-      <c r="B49" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>979</v>
+      </c>
+      <c r="B50" t="s">
         <v>980</v>
-      </c>
-      <c r="B50" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>981</v>
+      </c>
+      <c r="B51" t="s">
         <v>982</v>
-      </c>
-      <c r="B51" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>983</v>
+      </c>
+      <c r="B52" t="s">
         <v>984</v>
-      </c>
-      <c r="B52" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>985</v>
+      </c>
+      <c r="B53" t="s">
         <v>986</v>
-      </c>
-      <c r="B53" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B54" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>988</v>
+      </c>
+      <c r="B55" t="s">
         <v>989</v>
-      </c>
-      <c r="B55" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>990</v>
+      </c>
+      <c r="B56" t="s">
         <v>991</v>
-      </c>
-      <c r="B56" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>992</v>
+      </c>
+      <c r="B57" t="s">
         <v>993</v>
-      </c>
-      <c r="B57" t="s">
-        <v>994</v>
       </c>
     </row>
   </sheetData>
